--- a/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_12.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_12.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitter Model" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hitter Model'!$A$1:$EP$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hitter Model'!$A$1:$FR$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP31"/>
+  <dimension ref="A1:FR31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -658,7 +658,35 @@
     <col width="12" customWidth="1" min="143" max="143"/>
     <col width="12" customWidth="1" min="144" max="144"/>
     <col width="12" customWidth="1" min="145" max="145"/>
-    <col width="12" customWidth="1" min="146" max="146"/>
+    <col width="13" customWidth="1" min="146" max="146"/>
+    <col width="13" customWidth="1" min="147" max="147"/>
+    <col width="13" customWidth="1" min="148" max="148"/>
+    <col width="13" customWidth="1" min="149" max="149"/>
+    <col width="13" customWidth="1" min="150" max="150"/>
+    <col width="13" customWidth="1" min="151" max="151"/>
+    <col width="13" customWidth="1" min="152" max="152"/>
+    <col width="13" customWidth="1" min="153" max="153"/>
+    <col width="13" customWidth="1" min="154" max="154"/>
+    <col width="13" customWidth="1" min="155" max="155"/>
+    <col width="13" customWidth="1" min="156" max="156"/>
+    <col width="13" customWidth="1" min="157" max="157"/>
+    <col width="13" customWidth="1" min="158" max="158"/>
+    <col width="13" customWidth="1" min="159" max="159"/>
+    <col width="13" customWidth="1" min="160" max="160"/>
+    <col width="13" customWidth="1" min="161" max="161"/>
+    <col width="13" customWidth="1" min="162" max="162"/>
+    <col width="13" customWidth="1" min="163" max="163"/>
+    <col width="13" customWidth="1" min="164" max="164"/>
+    <col width="13" customWidth="1" min="165" max="165"/>
+    <col width="13" customWidth="1" min="166" max="166"/>
+    <col width="13" customWidth="1" min="167" max="167"/>
+    <col width="13" customWidth="1" min="168" max="168"/>
+    <col width="13" customWidth="1" min="169" max="169"/>
+    <col width="13" customWidth="1" min="170" max="170"/>
+    <col width="13" customWidth="1" min="171" max="171"/>
+    <col width="13" customWidth="1" min="172" max="172"/>
+    <col width="12" customWidth="1" min="173" max="173"/>
+    <col width="12" customWidth="1" min="174" max="174"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1389,7 +1417,147 @@
       </c>
       <c r="EP1" s="2" t="inlineStr">
         <is>
+          <t>Raw P Over 2.5 FS %</t>
+        </is>
+      </c>
+      <c r="EQ1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 3.0 FS %</t>
+        </is>
+      </c>
+      <c r="ER1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 3.5 FS %</t>
+        </is>
+      </c>
+      <c r="ES1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 4.0 FS %</t>
+        </is>
+      </c>
+      <c r="ET1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 4.5 FS %</t>
+        </is>
+      </c>
+      <c r="EU1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 5.0 FS %</t>
+        </is>
+      </c>
+      <c r="EV1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 5.5 FS %</t>
+        </is>
+      </c>
+      <c r="EW1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 6.0 FS %</t>
+        </is>
+      </c>
+      <c r="EX1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 6.5 FS %</t>
+        </is>
+      </c>
+      <c r="EY1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 7.0 FS %</t>
+        </is>
+      </c>
+      <c r="EZ1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 7.5 FS %</t>
+        </is>
+      </c>
+      <c r="FA1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 8.0 FS %</t>
+        </is>
+      </c>
+      <c r="FB1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 8.5 FS %</t>
+        </is>
+      </c>
+      <c r="FC1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 9.0 FS %</t>
+        </is>
+      </c>
+      <c r="FD1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 9.5 FS %</t>
+        </is>
+      </c>
+      <c r="FE1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 10.0 FS %</t>
+        </is>
+      </c>
+      <c r="FF1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 10.5 FS %</t>
+        </is>
+      </c>
+      <c r="FG1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 11.0 FS %</t>
+        </is>
+      </c>
+      <c r="FH1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 11.5 FS %</t>
+        </is>
+      </c>
+      <c r="FI1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 12.0 FS %</t>
+        </is>
+      </c>
+      <c r="FJ1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 12.5 FS %</t>
+        </is>
+      </c>
+      <c r="FK1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 13.0 FS %</t>
+        </is>
+      </c>
+      <c r="FL1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 13.5 FS %</t>
+        </is>
+      </c>
+      <c r="FM1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 14.0 FS %</t>
+        </is>
+      </c>
+      <c r="FN1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 14.5 FS %</t>
+        </is>
+      </c>
+      <c r="FO1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 15.0 FS %</t>
+        </is>
+      </c>
+      <c r="FP1" s="2" t="inlineStr">
+        <is>
+          <t>Raw P Over 15.5 FS %</t>
+        </is>
+      </c>
+      <c r="FQ1" s="2" t="inlineStr">
+        <is>
           <t>Confidence</t>
+        </is>
+      </c>
+      <c r="FR1" s="2" t="inlineStr">
+        <is>
+          <t>Full Game Projected FS</t>
         </is>
       </c>
     </row>
@@ -1874,14 +2042,96 @@
       </c>
       <c r="EO2" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP2" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP2" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="EQ2" s="3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="ER2" s="3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="ES2" s="3" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="ET2" s="3" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="EU2" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="EV2" s="3" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="EW2" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="EX2" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="EY2" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="EZ2" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="FA2" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="FB2" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="FC2" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="FD2" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="FE2" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="FF2" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="FG2" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FH2" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FI2" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="FJ2" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="FK2" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="FL2" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="FM2" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FN2" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FO2" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="FP2" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="FQ2" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1929,7 +2179,7 @@
         <v>11.44</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>10.2</v>
@@ -1965,34 +2215,34 @@
         <v>78.2</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="W3" s="5" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>64.7</v>
+        <v>64.8</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="AA3" s="6" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="AB3" s="7" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="AC3" s="7" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="AD3" s="7" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="AE3" s="7" t="n">
         <v>45.1</v>
@@ -2001,43 +2251,43 @@
         <v>45.1</v>
       </c>
       <c r="AG3" s="7" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="AH3" s="7" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="AI3" s="8" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="AJ3" s="8" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="AK3" s="8" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="AL3" s="8" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="AM3" s="8" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="AN3" s="8" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="AO3" s="8" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="AP3" s="8" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="AQ3" s="8" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AR3" s="8" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>278.44</v>
+        <v>278.62</v>
       </c>
       <c r="AT3" s="4" t="inlineStr">
         <is>
@@ -2358,14 +2608,96 @@
       </c>
       <c r="EO3" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP3" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP3" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="EQ3" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="ER3" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="ES3" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="ET3" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="EU3" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="EV3" s="3" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="EW3" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="EX3" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="EY3" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="EZ3" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="FA3" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="FB3" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="FC3" s="3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="FD3" s="3" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="FE3" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="FF3" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="FG3" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FH3" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FI3" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="FJ3" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="FK3" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="FL3" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="FM3" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="FN3" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="FO3" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FP3" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FQ3" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2848,14 +3180,96 @@
       </c>
       <c r="EO4" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP4" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP4" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="EQ4" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="ER4" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="ES4" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="ET4" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="EU4" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="EV4" s="3" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="EW4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="EX4" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="EY4" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="EZ4" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="FA4" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="FB4" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="FC4" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="FD4" s="3" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="FE4" s="3" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="FF4" s="3" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="FG4" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="FH4" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="FI4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="FJ4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="FK4" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="FL4" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="FM4" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FN4" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FO4" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FP4" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FQ4" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -2930,7 +3344,7 @@
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="S5" s="5" t="n">
         <v>75.40000000000001</v>
@@ -2945,10 +3359,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>62.3</v>
+        <v>62.4</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>58.9</v>
@@ -2981,10 +3395,10 @@
         <v>39.9</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="AK5" s="8" t="n">
         <v>35.6</v>
@@ -3332,14 +3746,96 @@
       </c>
       <c r="EO5" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP5" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP5" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="EQ5" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="ER5" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="ES5" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="ET5" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="EU5" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="EV5" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="EW5" s="3" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="EX5" s="3" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="EY5" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="EZ5" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="FA5" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="FB5" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="FC5" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="FD5" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="FE5" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="FF5" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="FG5" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="FH5" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="FI5" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FJ5" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FK5" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FL5" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FM5" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="FN5" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="FO5" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="FP5" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="FQ5" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -3822,14 +4318,96 @@
       </c>
       <c r="EO6" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP6" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP6" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="EQ6" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="ER6" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="ES6" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="ET6" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="EU6" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="EV6" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="EW6" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="EX6" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="EY6" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="EZ6" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="FA6" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="FB6" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="FC6" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="FD6" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="FE6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FF6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FG6" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="FH6" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="FI6" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="FJ6" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="FK6" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="FL6" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="FM6" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="FN6" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="FO6" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FP6" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FQ6" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -3919,10 +4497,10 @@
         <v>76.7</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>66.8</v>
+        <v>66.7</v>
       </c>
       <c r="Y7" s="5" t="n">
         <v>63.7</v>
@@ -3943,10 +4521,10 @@
         <v>50.9</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="AF7" s="7" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="AG7" s="7" t="n">
         <v>41.4</v>
@@ -3961,16 +4539,16 @@
         <v>38.6</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="AL7" s="8" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="AM7" s="8" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="AO7" s="8" t="n">
         <v>26.7</v>
@@ -4312,14 +4890,96 @@
       </c>
       <c r="EO7" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP7" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP7" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="EQ7" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="ER7" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="ES7" s="3" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="ET7" s="3" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="EU7" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="EV7" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="EW7" s="3" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="EX7" s="3" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="EY7" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="EZ7" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="FA7" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="FB7" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="FC7" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="FD7" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="FE7" s="3" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="FF7" s="3" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="FG7" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="FH7" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="FI7" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FJ7" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="FK7" s="3" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="FL7" s="3" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="FM7" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FN7" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FO7" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FP7" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FQ7" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -4367,7 +5027,7 @@
         <v>10.84</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>10</v>
@@ -4394,13 +5054,13 @@
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="U8" s="5" t="n">
         <v>71.5</v>
@@ -4409,46 +5069,46 @@
         <v>71.5</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>62.3</v>
+        <v>62.2</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="AA8" s="6" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="AB8" s="7" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="AC8" s="7" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="AD8" s="7" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="AE8" s="7" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="AG8" s="8" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AI8" s="8" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="AJ8" s="8" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="AK8" s="8" t="n">
         <v>32.4</v>
@@ -4457,10 +5117,10 @@
         <v>32.4</v>
       </c>
       <c r="AM8" s="8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="AO8" s="8" t="n">
         <v>26.2</v>
@@ -4475,7 +5135,7 @@
         <v>24.6</v>
       </c>
       <c r="AS8" s="3" t="n">
-        <v>261.15</v>
+        <v>260.98</v>
       </c>
       <c r="AT8" s="4" t="inlineStr">
         <is>
@@ -4783,7 +5443,7 @@
         <v>8</v>
       </c>
       <c r="EI8" s="3" t="n">
-        <v>8.52</v>
+        <v>8.51</v>
       </c>
       <c r="EJ8" s="3" t="n">
         <v>3</v>
@@ -4802,14 +5462,96 @@
       </c>
       <c r="EO8" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP8" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP8" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="EQ8" s="3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="ER8" s="3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="ES8" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="ET8" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="EU8" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="EV8" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="EW8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="EX8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="EY8" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="EZ8" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="FA8" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="FB8" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="FC8" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="FD8" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="FE8" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="FF8" s="3" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="FG8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="FH8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="FI8" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="FJ8" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="FK8" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="FL8" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="FM8" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="FN8" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="FO8" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FP8" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FQ8" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -4893,16 +5635,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="Y9" s="7" t="n">
         <v>51.7</v>
@@ -5286,14 +6028,96 @@
       </c>
       <c r="EO9" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP9" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP9" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="EQ9" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="ER9" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="ES9" s="3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="ET9" s="3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="EU9" s="3" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="EV9" s="3" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="EW9" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="EX9" s="3" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="EY9" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="EZ9" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="FA9" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="FB9" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="FC9" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="FD9" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="FE9" s="3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="FF9" s="3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="FG9" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="FH9" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="FI9" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="FJ9" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="FK9" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="FL9" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="FM9" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="FN9" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="FO9" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="FP9" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="FQ9" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -5341,7 +6165,7 @@
         <v>10.97</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>12.2</v>
@@ -5371,64 +6195,64 @@
         <v>74.8</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="X10" s="7" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="Y10" s="7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="Z10" s="7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="AA10" s="7" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AB10" s="7" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="AG10" s="8" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="AJ10" s="8" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="AM10" s="8" t="n">
         <v>28.3</v>
@@ -5449,7 +6273,7 @@
         <v>23.1</v>
       </c>
       <c r="AS10" s="3" t="n">
-        <v>251.43</v>
+        <v>251.54</v>
       </c>
       <c r="AT10" s="4" t="inlineStr">
         <is>
@@ -5776,14 +6600,96 @@
       </c>
       <c r="EO10" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP10" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP10" s="3" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="EQ10" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="ER10" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="ES10" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="ET10" s="3" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="EU10" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="EV10" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="EW10" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="EX10" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="EY10" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="EZ10" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="FA10" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="FB10" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="FC10" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FD10" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FE10" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="FF10" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="FG10" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="FH10" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="FI10" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="FJ10" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="FK10" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="FL10" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="FM10" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="FN10" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="FO10" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FP10" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FQ10" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -5831,7 +6737,7 @@
         <v>10.69</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11.2</v>
@@ -5861,10 +6767,10 @@
         <v>83.3</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="U11" s="5" t="n">
         <v>72.8</v>
@@ -5873,10 +6779,10 @@
         <v>72.8</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="Y11" s="5" t="n">
         <v>60.2</v>
@@ -5885,61 +6791,61 @@
         <v>60.2</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="AC11" s="7" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="AD11" s="7" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="AE11" s="7" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="AG11" s="8" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="AL11" s="8" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="AM11" s="8" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="AO11" s="8" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AQ11" s="8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AS11" s="3" t="n">
-        <v>248.54</v>
+        <v>248.38</v>
       </c>
       <c r="AT11" s="4" t="inlineStr">
         <is>
@@ -6241,7 +7147,7 @@
         <v>8</v>
       </c>
       <c r="EI11" s="3" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="EJ11" s="3" t="n">
         <v>4</v>
@@ -6260,14 +7166,96 @@
       </c>
       <c r="EO11" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP11" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP11" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="EQ11" s="3" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="ER11" s="3" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="ES11" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="ET11" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="EU11" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="EV11" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="EW11" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="EX11" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="EY11" s="3" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="EZ11" s="3" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="FA11" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="FB11" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="FC11" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="FD11" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="FE11" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="FF11" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="FG11" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="FH11" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="FI11" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="FJ11" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="FK11" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FL11" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FM11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FN11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FO11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FP11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FQ11" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -6750,14 +7738,96 @@
       </c>
       <c r="EO12" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP12" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP12" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="EQ12" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="ER12" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="ES12" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="ET12" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="EU12" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="EV12" s="3" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="EW12" s="3" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="EX12" s="3" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="EY12" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="EZ12" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="FA12" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="FB12" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="FC12" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="FD12" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="FE12" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="FF12" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="FG12" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="FH12" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="FI12" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FJ12" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FK12" s="3" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="FL12" s="3" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="FM12" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="FN12" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="FO12" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="FP12" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="FQ12" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -6805,7 +7875,7 @@
         <v>10.37</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>9.49</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>8</v>
@@ -6835,40 +7905,40 @@
         <v>83.90000000000001</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>62.4</v>
+        <v>62.3</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="AC13" s="7" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="AD13" s="7" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="AE13" s="7" t="n">
         <v>40.6</v>
@@ -6877,43 +7947,43 @@
         <v>40.6</v>
       </c>
       <c r="AG13" s="8" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="AJ13" s="8" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="AK13" s="8" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="AL13" s="8" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="AM13" s="8" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="AN13" s="8" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="AO13" s="8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AP13" s="8" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AQ13" s="8" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AR13" s="8" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AS13" s="3" t="n">
-        <v>243.9</v>
+        <v>243.73</v>
       </c>
       <c r="AT13" s="4" t="inlineStr">
         <is>
@@ -7234,14 +8304,96 @@
       </c>
       <c r="EO13" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP13" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP13" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="EQ13" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="ER13" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="ES13" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="ET13" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="EU13" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="EV13" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="EW13" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="EX13" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="EY13" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="EZ13" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="FA13" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="FB13" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="FC13" s="3" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="FD13" s="3" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="FE13" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FF13" s="3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="FG13" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="FH13" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="FI13" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="FJ13" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="FK13" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FL13" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FM13" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="FN13" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="FO13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="FP13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="FQ13" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -7331,10 +8483,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>58.7</v>
@@ -7343,22 +8495,22 @@
         <v>58.7</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="AD14" s="7" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="AG14" s="8" t="n">
         <v>32.3</v>
@@ -7397,7 +8549,7 @@
         <v>15</v>
       </c>
       <c r="AS14" s="3" t="n">
-        <v>238.61</v>
+        <v>238.59</v>
       </c>
       <c r="AT14" s="4" t="inlineStr">
         <is>
@@ -7724,14 +8876,96 @@
       </c>
       <c r="EO14" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP14" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP14" s="3" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="EQ14" s="3" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="ER14" s="3" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="ES14" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="ET14" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="EU14" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="EV14" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="EW14" s="3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="EX14" s="3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="EY14" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="EZ14" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="FA14" s="3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="FB14" s="3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="FC14" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="FD14" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="FE14" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="FF14" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="FG14" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="FH14" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="FI14" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="FJ14" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="FK14" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="FL14" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="FM14" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="FN14" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="FO14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="FP14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="FQ14" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -7839,10 +9073,10 @@
         <v>49.5</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="AE15" s="7" t="n">
         <v>40.5</v>
@@ -7863,10 +9097,10 @@
         <v>33</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="AM15" s="8" t="n">
         <v>27.8</v>
@@ -7875,19 +9109,19 @@
         <v>27.8</v>
       </c>
       <c r="AO15" s="8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AP15" s="8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AQ15" s="8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AR15" s="8" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AS15" s="3" t="n">
-        <v>237.9</v>
+        <v>237.89</v>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
@@ -8214,14 +9448,96 @@
       </c>
       <c r="EO15" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP15" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP15" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="EQ15" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="ER15" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="ES15" s="3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="ET15" s="3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="EU15" s="3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="EV15" s="3" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="EW15" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="EX15" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="EY15" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="EZ15" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="FA15" s="3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="FB15" s="3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="FC15" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="FD15" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="FE15" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="FF15" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="FG15" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="FH15" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="FI15" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="FJ15" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="FK15" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="FL15" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="FM15" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FN15" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FO15" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="FP15" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="FQ15" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -8704,14 +10020,96 @@
       </c>
       <c r="EO16" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP16" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP16" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="EQ16" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="ER16" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="ES16" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="ET16" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="EU16" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="EV16" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="EW16" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="EX16" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="EY16" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="EZ16" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="FA16" s="3" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="FB16" s="3" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="FC16" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="FD16" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="FE16" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="FF16" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="FG16" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FH16" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="FI16" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="FJ16" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="FK16" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="FL16" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="FM16" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="FN16" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="FO16" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="FP16" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="FQ16" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -9194,14 +10592,96 @@
       </c>
       <c r="EO17" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP17" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP17" s="3" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="EQ17" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="ER17" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="ES17" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="ET17" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="EU17" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="EV17" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="EW17" s="3" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="EX17" s="3" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="EY17" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="EZ17" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="FA17" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="FB17" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="FC17" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="FD17" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="FE17" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="FF17" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="FG17" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="FH17" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="FI17" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="FJ17" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="FK17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FL17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="FM17" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="FN17" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="FO17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="FP17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="FQ17" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -9249,7 +10729,7 @@
         <v>9.94</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8.69</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>5.6</v>
@@ -9276,25 +10756,25 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>61.5</v>
+        <v>61.6</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="X18" s="7" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="Y18" s="7" t="n">
         <v>48.4</v>
@@ -9309,16 +10789,16 @@
         <v>41.7</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="AG18" s="8" t="n">
         <v>30.9</v>
@@ -9357,7 +10837,7 @@
         <v>21.1</v>
       </c>
       <c r="AS18" s="3" t="n">
-        <v>233.05</v>
+        <v>233.11</v>
       </c>
       <c r="AT18" s="4" t="inlineStr">
         <is>
@@ -9659,7 +11139,7 @@
         <v>6</v>
       </c>
       <c r="EI18" s="3" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="EJ18" s="3" t="n">
         <v>2</v>
@@ -9678,14 +11158,96 @@
       </c>
       <c r="EO18" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP18" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP18" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="EQ18" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="ER18" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="ES18" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="ET18" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="EU18" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="EV18" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="EW18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="EX18" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="EY18" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="EZ18" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="FA18" s="3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="FB18" s="3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="FC18" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="FD18" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="FE18" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="FF18" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="FG18" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="FH18" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="FI18" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FJ18" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FK18" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FL18" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="FM18" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="FN18" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="FO18" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="FP18" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="FQ18" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -9701,22 +11263,22 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>HOU @ TEX</t>
+          <t>LAA @ MIN</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -9726,122 +11288,122 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>10.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.24</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6.93</v>
+        <v>8.6</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>2|0|20|5|0</t>
+          <t>9|7|7|21|3</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2|0|20|5|0|7|14|0|2|0</t>
+          <t>9|7|7|21|3|2|6|18|5|7</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2|0|20|5|0|7|14|0|2|0|7|2|20|6|19</t>
+          <t>9|7|7|21|3|2|6|18|5|7|30|0|9|0|5</t>
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>79</v>
+        <v>77.2</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>56.5</v>
+        <v>55.2</v>
       </c>
       <c r="X19" s="7" t="n">
-        <v>56.5</v>
+        <v>55.2</v>
       </c>
       <c r="Y19" s="7" t="n">
-        <v>53.4</v>
+        <v>51.2</v>
       </c>
       <c r="Z19" s="7" t="n">
-        <v>53.4</v>
+        <v>51.2</v>
       </c>
       <c r="AA19" s="7" t="n">
-        <v>45.6</v>
+        <v>43.2</v>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AC19" s="7" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="AD19" s="7" t="n">
-        <v>41.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="AC19" s="8" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AD19" s="8" t="n">
+        <v>39.4</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>37.4</v>
+        <v>34.5</v>
       </c>
       <c r="AF19" s="8" t="n">
-        <v>37.4</v>
+        <v>34.5</v>
       </c>
       <c r="AG19" s="8" t="n">
-        <v>33.8</v>
+        <v>30.9</v>
       </c>
       <c r="AH19" s="8" t="n">
-        <v>33.8</v>
+        <v>30.9</v>
       </c>
       <c r="AI19" s="8" t="n">
-        <v>31.5</v>
+        <v>28</v>
       </c>
       <c r="AJ19" s="8" t="n">
-        <v>31.5</v>
+        <v>28</v>
       </c>
       <c r="AK19" s="8" t="n">
-        <v>28.5</v>
+        <v>25.4</v>
       </c>
       <c r="AL19" s="8" t="n">
-        <v>28.5</v>
+        <v>25.4</v>
       </c>
       <c r="AM19" s="8" t="n">
-        <v>26.8</v>
+        <v>23.7</v>
       </c>
       <c r="AN19" s="8" t="n">
-        <v>26.8</v>
+        <v>23.7</v>
       </c>
       <c r="AO19" s="8" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="AP19" s="8" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="AQ19" s="8" t="n">
-        <v>22</v>
+        <v>18.9</v>
       </c>
       <c r="AR19" s="8" t="n">
-        <v>22</v>
+        <v>18.9</v>
       </c>
       <c r="AS19" s="3" t="n">
-        <v>230.68</v>
+        <v>231.96</v>
       </c>
       <c r="AT19" s="4" t="inlineStr">
         <is>
@@ -9850,11 +11412,11 @@
       </c>
       <c r="AU19" s="9" t="inlineStr">
         <is>
-          <t>Forecast 10.0 FS | Sim 9.2</t>
+          <t>Forecast 9.9 FS | Sim 8.6</t>
         </is>
       </c>
       <c r="AV19" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
@@ -9862,27 +11424,27 @@
         </is>
       </c>
       <c r="AX19" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY19" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ19" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BA19" s="4" t="inlineStr">
         <is>
-          <t>5-5-3-3-2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="BB19" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BC19" s="3" t="n">
         <v>100</v>
       </c>
       <c r="BD19" s="3" t="n">
-        <v>4.61</v>
+        <v>4.94</v>
       </c>
       <c r="BE19" s="4" t="inlineStr">
         <is>
@@ -9890,14 +11452,14 @@
         </is>
       </c>
       <c r="BF19" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG19" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BH19" s="4" t="inlineStr">
         <is>
-          <t>Cristian Javier</t>
+          <t>José Soriano</t>
         </is>
       </c>
       <c r="BI19" s="4" t="inlineStr">
@@ -9906,176 +11468,182 @@
         </is>
       </c>
       <c r="BJ19" s="3" t="n">
-        <v>9.98</v>
+        <v>3.49</v>
       </c>
       <c r="BK19" s="3" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="BL19" s="3" t="n">
-        <v>0.2532</v>
+        <v>0.1931</v>
       </c>
       <c r="BM19" s="3" t="n">
-        <v>0.038</v>
+        <v>0.0258</v>
       </c>
       <c r="BN19" s="3" t="n">
-        <v>0.1899</v>
+        <v>0.1137</v>
       </c>
       <c r="BO19" s="3" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="BP19" s="3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BQ19" s="3" t="n">
-        <v>0.2093</v>
+        <v>0.2058</v>
       </c>
       <c r="BR19" s="3" t="n">
-        <v>0.0363</v>
+        <v>0.0281</v>
       </c>
       <c r="BS19" s="4" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BT19" s="3" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="BU19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV19" s="4" t="n"/>
-      <c r="BW19" s="4" t="n"/>
-      <c r="BX19" s="4" t="n"/>
+        <v>1.055</v>
+      </c>
+      <c r="BV19" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BW19" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX19" s="3" t="n">
+        <v>223</v>
+      </c>
       <c r="BY19" s="4" t="n"/>
       <c r="BZ19" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="CA19" s="3" t="n">
-        <v>372</v>
+        <v>157</v>
       </c>
       <c r="CB19" s="3" t="n">
-        <v>338</v>
+        <v>130</v>
       </c>
       <c r="CC19" s="3" t="n">
-        <v>0.24</v>
+        <v>0.292</v>
       </c>
       <c r="CD19" s="3" t="n">
-        <v>0.304</v>
+        <v>0.404</v>
       </c>
       <c r="CE19" s="3" t="n">
-        <v>0.423</v>
+        <v>0.538</v>
       </c>
       <c r="CF19" s="3" t="n">
-        <v>0.727</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="CG19" s="3" t="n">
-        <v>292</v>
+        <v>99</v>
       </c>
       <c r="CH19" s="3" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="CI19" s="3" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="CJ19" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CK19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL19" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CM19" s="3" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="CN19" s="3" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="CO19" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CP19" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CQ19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CR19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS</t>
         </is>
       </c>
       <c r="CS19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS|2026-07-07 vs Los Angeles Angels: 7 FS|2026-07-05 vs Detroit Tigers: 14 FS|2026-07-02 vs Detroit Tigers: 0 FS|2026-07-01 @ Cleveland Guardians: 2 FS|2026-06-30 @ Cleveland Guardians: 0 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS</t>
         </is>
       </c>
       <c r="CT19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS|2026-07-07 vs Los Angeles Angels: 7 FS|2026-07-05 vs Detroit Tigers: 14 FS|2026-07-02 vs Detroit Tigers: 0 FS|2026-07-01 @ Cleveland Guardians: 2 FS|2026-06-30 @ Cleveland Guardians: 0 FS|2026-06-29 @ Cleveland Guardians: 7 FS|2026-06-28 @ Toronto Blue Jays: 2 FS|2026-06-27 @ Toronto Blue Jays: 20 FS|2026-06-26 @ Toronto Blue Jays: 6 FS|2026-06-25 @ Toronto Blue Jays: 19 FS</t>
+          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS|2026-05-07 @ Washington Nationals: 30 FS|2026-05-06 @ Washington Nationals: 0 FS|2026-05-05 @ Washington Nationals: 9 FS|2026-05-02 vs Toronto Blue Jays: 0 FS|2026-05-01 vs Toronto Blue Jays: 5 FS</t>
         </is>
       </c>
       <c r="CU19" s="3" t="n">
         <v>15</v>
       </c>
       <c r="CV19" s="3" t="n">
-        <v>6.86</v>
+        <v>7.86</v>
       </c>
       <c r="CW19" s="3" t="n">
-        <v>6.07</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="CX19" s="3" t="n">
-        <v>0.154</v>
+        <v>0.277</v>
       </c>
       <c r="CY19" s="4" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="CZ19" s="3" t="n">
-        <v>7.63</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DA19" s="3" t="n">
-        <v>1.466</v>
+        <v>2.214</v>
       </c>
       <c r="DB19" s="3" t="n">
-        <v>0.1379</v>
+        <v>0.2321</v>
       </c>
       <c r="DC19" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.1786</v>
       </c>
       <c r="DD19" s="3" t="n">
-        <v>0.0345</v>
+        <v>0.0536</v>
       </c>
       <c r="DE19" s="3" t="n">
-        <v>0.0862</v>
+        <v>0.1607</v>
       </c>
       <c r="DF19" s="3" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="DG19" s="3" t="n">
-        <v>239</v>
+        <v>31</v>
       </c>
       <c r="DH19" s="3" t="n">
-        <v>84.18000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="DI19" s="3" t="n">
-        <v>30.13</v>
+        <v>38.71</v>
       </c>
       <c r="DJ19" s="3" t="n">
-        <v>2.51</v>
+        <v>6.45</v>
       </c>
       <c r="DK19" s="3" t="n">
-        <v>25.94</v>
+        <v>32.26</v>
       </c>
       <c r="DL19" s="3" t="n">
-        <v>0.401</v>
+        <v>0.43</v>
       </c>
       <c r="DM19" s="3" t="n">
-        <v>0.9654</v>
+        <v>1.0755</v>
       </c>
       <c r="DN19" s="3" t="n">
         <v>1</v>
@@ -10087,10 +11655,10 @@
         <v>1</v>
       </c>
       <c r="DQ19" s="3" t="n">
-        <v>1.0361</v>
+        <v>1.16</v>
       </c>
       <c r="DR19" s="3" t="n">
-        <v>359</v>
+        <v>65</v>
       </c>
       <c r="DS19" s="4" t="inlineStr">
         <is>
@@ -10098,43 +11666,43 @@
         </is>
       </c>
       <c r="DT19" s="3" t="n">
-        <v>0.1677</v>
+        <v>0.1161</v>
       </c>
       <c r="DU19" s="3" t="n">
-        <v>0.0484</v>
+        <v>0.0594</v>
       </c>
       <c r="DV19" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0035</v>
       </c>
       <c r="DW19" s="3" t="n">
-        <v>0.0532</v>
+        <v>0.0418</v>
       </c>
       <c r="DX19" s="3" t="n">
-        <v>0.1099</v>
+        <v>0.1531</v>
       </c>
       <c r="DY19" s="3" t="n">
-        <v>0.014</v>
+        <v>0.0129</v>
       </c>
       <c r="DZ19" s="3" t="n">
-        <v>0.2309</v>
+        <v>0.1859</v>
       </c>
       <c r="EA19" s="3" t="n">
-        <v>0.4545</v>
+        <v>0.3889</v>
       </c>
       <c r="EB19" s="3" t="n">
-        <v>0.3223</v>
+        <v>0.3333</v>
       </c>
       <c r="EC19" s="3" t="n">
-        <v>0.2232</v>
+        <v>0.2778</v>
       </c>
       <c r="ED19" s="3" t="n">
-        <v>0.1133</v>
+        <v>0.1385</v>
       </c>
       <c r="EE19" s="3" t="n">
-        <v>0.1742</v>
+        <v>0.1318</v>
       </c>
       <c r="EF19" s="3" t="n">
-        <v>0.0097</v>
+        <v>0.0104</v>
       </c>
       <c r="EG19" s="3" t="n">
         <v>1</v>
@@ -10143,33 +11711,115 @@
         <v>7</v>
       </c>
       <c r="EI19" s="3" t="n">
-        <v>8.24</v>
+        <v>7.64</v>
       </c>
       <c r="EJ19" s="3" t="n">
         <v>3</v>
       </c>
       <c r="EK19" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="EL19" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EM19" s="3" t="n">
-        <v>4.31</v>
+        <v>4.47</v>
       </c>
       <c r="EN19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="EO19" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP19" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP19" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="EQ19" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="ER19" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="ES19" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="ET19" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="EU19" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="EV19" s="3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="EW19" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="EX19" s="3" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="EY19" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="EZ19" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="FA19" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="FB19" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="FC19" s="3" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="FD19" s="3" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="FE19" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="FF19" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="FG19" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="FH19" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="FI19" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="FJ19" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="FK19" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FL19" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="FM19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="FN19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="FO19" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="FP19" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="FQ19" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -10185,22 +11835,22 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>LAA @ MIN</t>
+          <t>HOU @ TEX</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -10210,122 +11860,122 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>8.6</v>
+        <v>6.93</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>9|7|7|21|3</t>
+          <t>2|0|20|5|0</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>9|7|7|21|3|2|6|18|5|7</t>
+          <t>2|0|20|5|0|7|14|0|2|0</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>9|7|7|21|3|2|6|18|5|7|30|0|9|0|5</t>
+          <t>2|0|20|5|0|7|14|0|2|0|7|2|20|6|19</t>
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>69.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>69.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>63.4</v>
+        <v>66.8</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>63.4</v>
+        <v>66.8</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>53.9</v>
+        <v>56.4</v>
       </c>
       <c r="X20" s="7" t="n">
-        <v>53.9</v>
+        <v>56.4</v>
       </c>
       <c r="Y20" s="7" t="n">
-        <v>50.1</v>
+        <v>53.3</v>
       </c>
       <c r="Z20" s="7" t="n">
-        <v>50.1</v>
+        <v>53.3</v>
       </c>
       <c r="AA20" s="7" t="n">
-        <v>42.4</v>
+        <v>45.6</v>
       </c>
       <c r="AB20" s="7" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="AC20" s="8" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="AD20" s="8" t="n">
-        <v>38.7</v>
+        <v>45.6</v>
+      </c>
+      <c r="AC20" s="7" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AD20" s="7" t="n">
+        <v>41.7</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>33.8</v>
+        <v>37.3</v>
       </c>
       <c r="AF20" s="8" t="n">
-        <v>33.8</v>
+        <v>37.3</v>
       </c>
       <c r="AG20" s="8" t="n">
-        <v>30.1</v>
+        <v>33.7</v>
       </c>
       <c r="AH20" s="8" t="n">
-        <v>30.1</v>
+        <v>33.7</v>
       </c>
       <c r="AI20" s="8" t="n">
-        <v>27.1</v>
+        <v>31.4</v>
       </c>
       <c r="AJ20" s="8" t="n">
-        <v>27.1</v>
+        <v>31.4</v>
       </c>
       <c r="AK20" s="8" t="n">
-        <v>24.5</v>
+        <v>28.4</v>
       </c>
       <c r="AL20" s="8" t="n">
-        <v>24.5</v>
+        <v>28.4</v>
       </c>
       <c r="AM20" s="8" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="AN20" s="8" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="AO20" s="8" t="n">
-        <v>19.3</v>
+        <v>22.8</v>
       </c>
       <c r="AP20" s="8" t="n">
-        <v>19.3</v>
+        <v>22.8</v>
       </c>
       <c r="AQ20" s="8" t="n">
-        <v>18.2</v>
+        <v>22</v>
       </c>
       <c r="AR20" s="8" t="n">
-        <v>18.2</v>
+        <v>22</v>
       </c>
       <c r="AS20" s="3" t="n">
-        <v>230.4</v>
+        <v>230.66</v>
       </c>
       <c r="AT20" s="4" t="inlineStr">
         <is>
@@ -10334,11 +11984,11 @@
       </c>
       <c r="AU20" s="9" t="inlineStr">
         <is>
-          <t>Forecast 9.9 FS | Sim 8.4</t>
+          <t>Forecast 10.0 FS | Sim 9.2</t>
         </is>
       </c>
       <c r="AV20" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
@@ -10346,27 +11996,27 @@
         </is>
       </c>
       <c r="AX20" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY20" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AZ20" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BA20" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5-5-3-3-2</t>
         </is>
       </c>
       <c r="BB20" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="BC20" s="3" t="n">
         <v>100</v>
       </c>
       <c r="BD20" s="3" t="n">
-        <v>4.94</v>
+        <v>4.61</v>
       </c>
       <c r="BE20" s="4" t="inlineStr">
         <is>
@@ -10374,14 +12024,14 @@
         </is>
       </c>
       <c r="BF20" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG20" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="BH20" s="4" t="inlineStr">
         <is>
-          <t>José Soriano</t>
+          <t>Cristian Javier</t>
         </is>
       </c>
       <c r="BI20" s="4" t="inlineStr">
@@ -10390,182 +12040,176 @@
         </is>
       </c>
       <c r="BJ20" s="3" t="n">
-        <v>3.49</v>
+        <v>9.98</v>
       </c>
       <c r="BK20" s="3" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="BL20" s="3" t="n">
-        <v>0.1931</v>
+        <v>0.2532</v>
       </c>
       <c r="BM20" s="3" t="n">
-        <v>0.0258</v>
+        <v>0.038</v>
       </c>
       <c r="BN20" s="3" t="n">
-        <v>0.1137</v>
+        <v>0.1899</v>
       </c>
       <c r="BO20" s="3" t="n">
-        <v>4.65</v>
+        <v>4.81</v>
       </c>
       <c r="BP20" s="3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BQ20" s="3" t="n">
-        <v>0.2058</v>
+        <v>0.2093</v>
       </c>
       <c r="BR20" s="3" t="n">
-        <v>0.0281</v>
+        <v>0.0363</v>
       </c>
       <c r="BS20" s="4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BT20" s="3" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="BU20" s="3" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="BV20" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="BW20" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX20" s="3" t="n">
-        <v>223</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BV20" s="4" t="n"/>
+      <c r="BW20" s="4" t="n"/>
+      <c r="BX20" s="4" t="n"/>
       <c r="BY20" s="4" t="n"/>
       <c r="BZ20" s="4" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="CA20" s="3" t="n">
-        <v>157</v>
+        <v>372</v>
       </c>
       <c r="CB20" s="3" t="n">
-        <v>130</v>
+        <v>338</v>
       </c>
       <c r="CC20" s="3" t="n">
-        <v>0.292</v>
+        <v>0.24</v>
       </c>
       <c r="CD20" s="3" t="n">
-        <v>0.404</v>
+        <v>0.304</v>
       </c>
       <c r="CE20" s="3" t="n">
-        <v>0.538</v>
+        <v>0.423</v>
       </c>
       <c r="CF20" s="3" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.727</v>
       </c>
       <c r="CG20" s="3" t="n">
-        <v>99</v>
+        <v>292</v>
       </c>
       <c r="CH20" s="3" t="n">
-        <v>0.944</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="CI20" s="3" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="CJ20" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CK20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL20" s="3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CM20" s="3" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="CN20" s="3" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="CO20" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="CP20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CQ20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CR20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS</t>
+          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS</t>
         </is>
       </c>
       <c r="CS20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS</t>
+          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS|2026-07-07 vs Los Angeles Angels: 7 FS|2026-07-05 vs Detroit Tigers: 14 FS|2026-07-02 vs Detroit Tigers: 0 FS|2026-07-01 @ Cleveland Guardians: 2 FS|2026-06-30 @ Cleveland Guardians: 0 FS</t>
         </is>
       </c>
       <c r="CT20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Los Angeles Angels: 9 FS|2026-07-10 vs Los Angeles Angels: 7 FS|2026-05-18 vs Houston Astros: 7 FS|2026-05-17 vs Milwaukee Brewers: 21 FS|2026-05-16 vs Milwaukee Brewers: 3 FS|2026-05-15 vs Milwaukee Brewers: 2 FS|2026-05-14 vs Miami Marlins: 6 FS|2026-05-12 vs Miami Marlins: 18 FS|2026-05-10 @ Cleveland Guardians: 5 FS|2026-05-08 @ Cleveland Guardians: 7 FS|2026-05-07 @ Washington Nationals: 30 FS|2026-05-06 @ Washington Nationals: 0 FS|2026-05-05 @ Washington Nationals: 9 FS|2026-05-02 vs Toronto Blue Jays: 0 FS|2026-05-01 vs Toronto Blue Jays: 5 FS</t>
+          <t>2026-07-12 vs Houston Astros: 2 FS|2026-07-11 vs Houston Astros: 0 FS|2026-07-10 vs Houston Astros: 20 FS|2026-07-09 vs Los Angeles Angels: 5 FS|2026-07-08 vs Los Angeles Angels: 0 FS|2026-07-07 vs Los Angeles Angels: 7 FS|2026-07-05 vs Detroit Tigers: 14 FS|2026-07-02 vs Detroit Tigers: 0 FS|2026-07-01 @ Cleveland Guardians: 2 FS|2026-06-30 @ Cleveland Guardians: 0 FS|2026-06-29 @ Cleveland Guardians: 7 FS|2026-06-28 @ Toronto Blue Jays: 2 FS|2026-06-27 @ Toronto Blue Jays: 20 FS|2026-06-26 @ Toronto Blue Jays: 6 FS|2026-06-25 @ Toronto Blue Jays: 19 FS</t>
         </is>
       </c>
       <c r="CU20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="CV20" s="3" t="n">
-        <v>7.86</v>
+        <v>6.86</v>
       </c>
       <c r="CW20" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>6.07</v>
       </c>
       <c r="CX20" s="3" t="n">
-        <v>0.277</v>
+        <v>0.154</v>
       </c>
       <c r="CY20" s="4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="CZ20" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="DA20" s="3" t="n">
-        <v>2.214</v>
+        <v>1.466</v>
       </c>
       <c r="DB20" s="3" t="n">
-        <v>0.2321</v>
+        <v>0.1379</v>
       </c>
       <c r="DC20" s="3" t="n">
-        <v>0.1786</v>
+        <v>0.0345</v>
       </c>
       <c r="DD20" s="3" t="n">
-        <v>0.0536</v>
+        <v>0.0345</v>
       </c>
       <c r="DE20" s="3" t="n">
-        <v>0.1607</v>
+        <v>0.0862</v>
       </c>
       <c r="DF20" s="3" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="DG20" s="3" t="n">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="DH20" s="3" t="n">
-        <v>86.81</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="DI20" s="3" t="n">
-        <v>38.71</v>
+        <v>30.13</v>
       </c>
       <c r="DJ20" s="3" t="n">
-        <v>6.45</v>
+        <v>2.51</v>
       </c>
       <c r="DK20" s="3" t="n">
-        <v>32.26</v>
+        <v>25.94</v>
       </c>
       <c r="DL20" s="3" t="n">
-        <v>0.43</v>
+        <v>0.401</v>
       </c>
       <c r="DM20" s="3" t="n">
-        <v>1.0755</v>
+        <v>0.9654</v>
       </c>
       <c r="DN20" s="3" t="n">
         <v>1</v>
@@ -10577,10 +12221,10 @@
         <v>1</v>
       </c>
       <c r="DQ20" s="3" t="n">
-        <v>1.16</v>
+        <v>1.0361</v>
       </c>
       <c r="DR20" s="3" t="n">
-        <v>65</v>
+        <v>359</v>
       </c>
       <c r="DS20" s="4" t="inlineStr">
         <is>
@@ -10588,43 +12232,43 @@
         </is>
       </c>
       <c r="DT20" s="3" t="n">
-        <v>0.1161</v>
+        <v>0.1677</v>
       </c>
       <c r="DU20" s="3" t="n">
-        <v>0.0594</v>
+        <v>0.0484</v>
       </c>
       <c r="DV20" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0031</v>
       </c>
       <c r="DW20" s="3" t="n">
-        <v>0.0418</v>
+        <v>0.0532</v>
       </c>
       <c r="DX20" s="3" t="n">
-        <v>0.1531</v>
+        <v>0.1099</v>
       </c>
       <c r="DY20" s="3" t="n">
-        <v>0.0129</v>
+        <v>0.014</v>
       </c>
       <c r="DZ20" s="3" t="n">
-        <v>0.1859</v>
+        <v>0.2309</v>
       </c>
       <c r="EA20" s="3" t="n">
-        <v>0.3889</v>
+        <v>0.4545</v>
       </c>
       <c r="EB20" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.3223</v>
       </c>
       <c r="EC20" s="3" t="n">
-        <v>0.2778</v>
+        <v>0.2232</v>
       </c>
       <c r="ED20" s="3" t="n">
-        <v>0.1385</v>
+        <v>0.1133</v>
       </c>
       <c r="EE20" s="3" t="n">
-        <v>0.1318</v>
+        <v>0.1742</v>
       </c>
       <c r="EF20" s="3" t="n">
-        <v>0.0104</v>
+        <v>0.0097</v>
       </c>
       <c r="EG20" s="3" t="n">
         <v>1</v>
@@ -10633,33 +12277,115 @@
         <v>7</v>
       </c>
       <c r="EI20" s="3" t="n">
-        <v>7.61</v>
+        <v>8.25</v>
       </c>
       <c r="EJ20" s="3" t="n">
         <v>3</v>
       </c>
       <c r="EK20" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EL20" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="EM20" s="3" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="EN20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="EO20" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP20" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP20" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="EQ20" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="ER20" s="3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="ES20" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="ET20" s="3" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="EU20" s="3" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="EV20" s="3" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="EW20" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="EX20" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="EY20" s="3" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="EZ20" s="3" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="FA20" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="FB20" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="FC20" s="3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="FD20" s="3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="FE20" s="3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="FF20" s="3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="FG20" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="FH20" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="FI20" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FJ20" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FK20" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FL20" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FM20" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="FN20" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="FO20" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="FP20" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="FQ20" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -10737,10 +12463,10 @@
         <v>73.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="U21" s="5" t="n">
         <v>61.2</v>
@@ -10761,10 +12487,10 @@
         <v>49.1</v>
       </c>
       <c r="AA21" s="7" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="AC21" s="8" t="n">
         <v>38.5</v>
@@ -10791,10 +12517,10 @@
         <v>28.4</v>
       </c>
       <c r="AK21" s="8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="AL21" s="8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="AM21" s="8" t="n">
         <v>24.3</v>
@@ -10803,10 +12529,10 @@
         <v>24.3</v>
       </c>
       <c r="AO21" s="8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AP21" s="8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AQ21" s="8" t="n">
         <v>19.4</v>
@@ -10815,7 +12541,7 @@
         <v>19.4</v>
       </c>
       <c r="AS21" s="3" t="n">
-        <v>229.75</v>
+        <v>229.74</v>
       </c>
       <c r="AT21" s="4" t="inlineStr">
         <is>
@@ -11117,7 +12843,7 @@
         <v>6</v>
       </c>
       <c r="EI21" s="3" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="EJ21" s="3" t="n">
         <v>2</v>
@@ -11136,14 +12862,96 @@
       </c>
       <c r="EO21" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP21" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP21" s="3" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="EQ21" s="3" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="ER21" s="3" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="ES21" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="ET21" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="EU21" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="EV21" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="EW21" s="3" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="EX21" s="3" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="EY21" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="EZ21" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="FA21" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="FB21" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="FC21" s="3" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="FD21" s="3" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="FE21" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="FF21" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="FG21" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FH21" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="FI21" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FJ21" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FK21" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="FL21" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="FM21" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="FN21" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="FO21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="FP21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="FQ21" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -11626,14 +13434,96 @@
       </c>
       <c r="EO22" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP22" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP22" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="EQ22" s="3" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="ER22" s="3" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="ES22" s="3" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="ET22" s="3" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="EU22" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="EV22" s="3" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="EW22" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="EX22" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="EY22" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="EZ22" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="FA22" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="FB22" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="FC22" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="FD22" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="FE22" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="FF22" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="FG22" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="FH22" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="FI22" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FJ22" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FK22" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="FL22" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="FM22" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="FN22" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="FO22" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="FP22" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="FQ22" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -11649,147 +13539,147 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Mike Trout</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>SEA @ TB</t>
+          <t>LAA @ MIN</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.42</v>
+        <v>9.52</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.38</v>
+        <v>7.96</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>11.8</v>
+        <v>9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>11.73</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>2|16|25|16|0</t>
+          <t>6|10|4|20|5</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2|16|25|16|0|0|0|2|26|14</t>
+          <t>6|10|4|20|5|23|21|5|8|9</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2|16|25|16|0|0|0|2|26|14|0|16|21|24|14</t>
+          <t>6|10|4|20|5|23|21|5|8|9|21|9|2|0|0</t>
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="T23" s="7" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U23" s="7" t="n">
-        <v>51.5</v>
+        <v>71.8</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>57.6</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>51.5</v>
+        <v>57.6</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>42.4</v>
+        <v>49</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="Y23" s="8" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Z23" s="8" t="n">
-        <v>39.7</v>
+        <v>49</v>
+      </c>
+      <c r="Y23" s="7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="Z23" s="7" t="n">
+        <v>44.9</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>34.7</v>
+        <v>37.9</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>34.7</v>
+        <v>37.9</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="AD23" s="8" t="n">
-        <v>32.1</v>
+        <v>34.5</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="AG23" s="8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AH23" s="8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AI23" s="8" t="n">
-        <v>26.7</v>
+        <v>25.8</v>
       </c>
       <c r="AJ23" s="8" t="n">
-        <v>26.7</v>
+        <v>25.8</v>
       </c>
       <c r="AK23" s="8" t="n">
-        <v>25.4</v>
+        <v>24.1</v>
       </c>
       <c r="AL23" s="8" t="n">
-        <v>25.4</v>
+        <v>24.1</v>
       </c>
       <c r="AM23" s="8" t="n">
-        <v>24.9</v>
+        <v>23.1</v>
       </c>
       <c r="AN23" s="8" t="n">
-        <v>24.9</v>
+        <v>23.1</v>
       </c>
       <c r="AO23" s="8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP23" s="8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ23" s="8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AR23" s="8" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AS23" s="3" t="n">
-        <v>222.07</v>
+        <v>222.2</v>
       </c>
       <c r="AT23" s="4" t="inlineStr">
         <is>
@@ -11798,29 +13688,29 @@
       </c>
       <c r="AU23" s="9" t="inlineStr">
         <is>
-          <t>Forecast 9.4 FS | Sim 7.4</t>
+          <t>Forecast 9.5 FS | Sim 8.0</t>
         </is>
       </c>
       <c r="AV23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW23" s="4" t="inlineStr">
+        <is>
+          <t>Today Posted</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AW23" s="4" t="inlineStr">
-        <is>
-          <t>Today Posted</t>
-        </is>
-      </c>
-      <c r="AX23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ23" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="BA23" s="4" t="inlineStr">
         <is>
-          <t>3-3-3-3-3-3-3</t>
+          <t>2-2-2</t>
         </is>
       </c>
       <c r="BB23" s="3" t="n">
@@ -11830,7 +13720,7 @@
         <v>100</v>
       </c>
       <c r="BD23" s="3" t="n">
-        <v>4.92</v>
+        <v>5.02</v>
       </c>
       <c r="BE23" s="4" t="inlineStr">
         <is>
@@ -11845,7 +13735,7 @@
       </c>
       <c r="BH23" s="4" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="BI23" s="4" t="inlineStr">
@@ -11854,129 +13744,135 @@
         </is>
       </c>
       <c r="BJ23" s="3" t="n">
-        <v>3.17</v>
+        <v>3.59</v>
       </c>
       <c r="BK23" s="3" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BL23" s="3" t="n">
-        <v>0.1923</v>
+        <v>0.1972</v>
       </c>
       <c r="BM23" s="3" t="n">
-        <v>0.0308</v>
+        <v>0.0348</v>
       </c>
       <c r="BN23" s="3" t="n">
-        <v>0.0641</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="BO23" s="3" t="n">
-        <v>3.61</v>
+        <v>4.62</v>
       </c>
       <c r="BP23" s="3" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="BQ23" s="3" t="n">
-        <v>0.2176</v>
+        <v>0.2211</v>
       </c>
       <c r="BR23" s="3" t="n">
-        <v>0.0254</v>
+        <v>0.0307</v>
       </c>
       <c r="BS23" s="4" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BT23" s="3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="BU23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV23" s="4" t="n"/>
-      <c r="BW23" s="4" t="n"/>
-      <c r="BX23" s="4" t="n"/>
+        <v>1.055</v>
+      </c>
+      <c r="BV23" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BW23" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX23" s="3" t="n">
+        <v>223</v>
+      </c>
       <c r="BY23" s="4" t="n"/>
       <c r="BZ23" s="4" t="inlineStr">
         <is>
-          <t>Indoor/retractable neutral</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="CA23" s="3" t="n">
-        <v>411</v>
+        <v>354</v>
       </c>
       <c r="CB23" s="3" t="n">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="CC23" s="3" t="n">
-        <v>0.279</v>
+        <v>0.237</v>
       </c>
       <c r="CD23" s="3" t="n">
-        <v>0.372</v>
+        <v>0.39</v>
       </c>
       <c r="CE23" s="3" t="n">
-        <v>0.555</v>
+        <v>0.473</v>
       </c>
       <c r="CF23" s="3" t="n">
-        <v>0.927</v>
+        <v>0.863</v>
       </c>
       <c r="CG23" s="3" t="n">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="CH23" s="3" t="n">
-        <v>0.891</v>
+        <v>0.865</v>
       </c>
       <c r="CI23" s="3" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="CJ23" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CK23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CL23" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="CM23" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="CN23" s="3" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="CO23" s="3" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="CP23" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CQ23" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CR23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS</t>
+          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS</t>
         </is>
       </c>
       <c r="CS23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS|2026-07-07 vs New York Yankees: 0 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 2 FS|2026-07-04 @ Houston Astros: 26 FS|2026-07-03 @ Houston Astros: 14 FS</t>
+          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS|2026-06-16 @ Arizona Diamondbacks: 23 FS|2026-06-15 @ Arizona Diamondbacks: 21 FS|2026-06-14 vs Tampa Bay Rays: 5 FS|2026-06-13 vs Tampa Bay Rays: 8 FS|2026-06-12 vs Tampa Bay Rays: 9 FS</t>
         </is>
       </c>
       <c r="CT23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS|2026-07-07 vs New York Yankees: 0 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 2 FS|2026-07-04 @ Houston Astros: 26 FS|2026-07-03 @ Houston Astros: 14 FS|2026-07-02 @ Kansas City Royals: 0 FS|2026-07-01 @ Kansas City Royals: 16 FS|2026-06-30 @ Kansas City Royals: 21 FS|2026-06-28 vs Arizona Diamondbacks: 24 FS|2026-06-27 vs Arizona Diamondbacks: 14 FS</t>
+          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS|2026-06-16 @ Arizona Diamondbacks: 23 FS|2026-06-15 @ Arizona Diamondbacks: 21 FS|2026-06-14 vs Tampa Bay Rays: 5 FS|2026-06-13 vs Tampa Bay Rays: 8 FS|2026-06-12 vs Tampa Bay Rays: 9 FS|2026-06-10 vs Houston Astros: 21 FS|2026-06-09 vs Houston Astros: 9 FS|2026-06-08 vs Houston Astros: 2 FS|2026-06-07 @ Los Angeles Dodgers: 0 FS|2026-06-06 @ Los Angeles Dodgers: 0 FS</t>
         </is>
       </c>
       <c r="CU23" s="3" t="n">
         <v>15</v>
       </c>
       <c r="CV23" s="3" t="n">
-        <v>8.43</v>
+        <v>12.71</v>
       </c>
       <c r="CW23" s="3" t="n">
-        <v>11.57</v>
+        <v>10.21</v>
       </c>
       <c r="CX23" s="3" t="n">
-        <v>0.245</v>
+        <v>0.254</v>
       </c>
       <c r="CY23" s="4" t="inlineStr">
         <is>
@@ -11984,46 +13880,46 @@
         </is>
       </c>
       <c r="CZ23" s="3" t="n">
-        <v>11.27</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="DA23" s="3" t="n">
-        <v>2.656</v>
+        <v>2.134</v>
       </c>
       <c r="DB23" s="3" t="n">
-        <v>0.2131</v>
+        <v>0.2239</v>
       </c>
       <c r="DC23" s="3" t="n">
-        <v>0.1475</v>
+        <v>0.1045</v>
       </c>
       <c r="DD23" s="3" t="n">
-        <v>0.1148</v>
+        <v>0.0597</v>
       </c>
       <c r="DE23" s="3" t="n">
-        <v>0.1148</v>
+        <v>0.1045</v>
       </c>
       <c r="DF23" s="3" t="n">
-        <v>0.0328</v>
+        <v>0.0299</v>
       </c>
       <c r="DG23" s="3" t="n">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="DH23" s="3" t="n">
-        <v>88.03</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="DI23" s="3" t="n">
-        <v>41</v>
+        <v>24.62</v>
       </c>
       <c r="DJ23" s="3" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="DK23" s="3" t="n">
-        <v>27.59</v>
+        <v>30.15</v>
       </c>
       <c r="DL23" s="3" t="n">
-        <v>0.433</v>
+        <v>0.456</v>
       </c>
       <c r="DM23" s="3" t="n">
-        <v>1.0756</v>
+        <v>0.9715</v>
       </c>
       <c r="DN23" s="3" t="n">
         <v>1</v>
@@ -12035,10 +13931,10 @@
         <v>1</v>
       </c>
       <c r="DQ23" s="3" t="n">
-        <v>1.0826</v>
+        <v>1.058</v>
       </c>
       <c r="DR23" s="3" t="n">
-        <v>620</v>
+        <v>431</v>
       </c>
       <c r="DS23" s="4" t="inlineStr">
         <is>
@@ -12046,43 +13942,43 @@
         </is>
       </c>
       <c r="DT23" s="3" t="n">
-        <v>0.1131</v>
+        <v>0.1061</v>
       </c>
       <c r="DU23" s="3" t="n">
-        <v>0.0364</v>
+        <v>0.0395</v>
       </c>
       <c r="DV23" s="3" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="DW23" s="3" t="n">
-        <v>0.0599</v>
+        <v>0.0473</v>
       </c>
       <c r="DX23" s="3" t="n">
-        <v>0.0823</v>
+        <v>0.1504</v>
       </c>
       <c r="DY23" s="3" t="n">
-        <v>0.0064</v>
+        <v>0.0127</v>
       </c>
       <c r="DZ23" s="3" t="n">
-        <v>0.2081</v>
+        <v>0.2484</v>
       </c>
       <c r="EA23" s="3" t="n">
-        <v>0.5238</v>
+        <v>0.3667</v>
       </c>
       <c r="EB23" s="3" t="n">
-        <v>0.2518</v>
+        <v>0.3556</v>
       </c>
       <c r="EC23" s="3" t="n">
-        <v>0.2244</v>
+        <v>0.2778</v>
       </c>
       <c r="ED23" s="3" t="n">
-        <v>0.1242</v>
+        <v>0.1368</v>
       </c>
       <c r="EE23" s="3" t="n">
-        <v>0.1494</v>
+        <v>0.1086</v>
       </c>
       <c r="EF23" s="3" t="n">
-        <v>0.0107</v>
+        <v>0.0144</v>
       </c>
       <c r="EG23" s="3" t="n">
         <v>1</v>
@@ -12091,33 +13987,115 @@
         <v>5</v>
       </c>
       <c r="EI23" s="3" t="n">
-        <v>7.97</v>
+        <v>7.71</v>
       </c>
       <c r="EJ23" s="3" t="n">
         <v>2</v>
       </c>
       <c r="EK23" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="EL23" s="3" t="n">
         <v>19</v>
       </c>
       <c r="EM23" s="3" t="n">
-        <v>4.16</v>
+        <v>4.39</v>
       </c>
       <c r="EN23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="EO23" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP23" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP23" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="EQ23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="ER23" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="ES23" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="ET23" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="EU23" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="EV23" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="EW23" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="EX23" s="3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="EY23" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="EZ23" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="FA23" s="3" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="FB23" s="3" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="FC23" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="FD23" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="FE23" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="FF23" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="FG23" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FH23" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="FI23" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="FJ23" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="FK23" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FL23" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FM23" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="FN23" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="FO23" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="FP23" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="FQ23" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -12133,147 +14111,147 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Mike Trout</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>LAA @ MIN</t>
+          <t>SEA @ TB</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>9.52</v>
+        <v>9.42</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>7.93</v>
+        <v>7.38</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>9</v>
+        <v>11.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>11.1</v>
+        <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>11.73</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>6|10|4|20|5</t>
+          <t>2|16|25|16|0</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>6|10|4|20|5|23|21|5|8|9</t>
+          <t>2|16|25|16|0|0|0|2|26|14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>6|10|4|20|5|23|21|5|8|9|21|9|2|0|0</t>
+          <t>2|16|25|16|0|0|0|2|26|14|0|16|21|24|14</t>
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="U24" s="6" t="n">
-        <v>57.5</v>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="T24" s="7" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>51.5</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>57.5</v>
+        <v>51.5</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>48.8</v>
+        <v>42.4</v>
       </c>
       <c r="X24" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="Y24" s="7" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="Z24" s="7" t="n">
-        <v>44.8</v>
+        <v>42.4</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>34.4</v>
+        <v>32.1</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="AG24" s="8" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="AH24" s="8" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="AI24" s="8" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
       <c r="AJ24" s="8" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
       <c r="AK24" s="8" t="n">
-        <v>24</v>
+        <v>25.4</v>
       </c>
       <c r="AL24" s="8" t="n">
-        <v>24</v>
+        <v>25.4</v>
       </c>
       <c r="AM24" s="8" t="n">
-        <v>23</v>
+        <v>24.9</v>
       </c>
       <c r="AN24" s="8" t="n">
-        <v>23</v>
+        <v>24.9</v>
       </c>
       <c r="AO24" s="8" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="AP24" s="8" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="AQ24" s="8" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AR24" s="8" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AS24" s="3" t="n">
-        <v>221.94</v>
+        <v>222.07</v>
       </c>
       <c r="AT24" s="4" t="inlineStr">
         <is>
@@ -12282,11 +14260,11 @@
       </c>
       <c r="AU24" s="9" t="inlineStr">
         <is>
-          <t>Forecast 9.5 FS | Sim 7.9</t>
+          <t>Forecast 9.4 FS | Sim 7.4</t>
         </is>
       </c>
       <c r="AV24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
@@ -12294,17 +14272,17 @@
         </is>
       </c>
       <c r="AX24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ24" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA24" s="4" t="inlineStr">
         <is>
-          <t>2-2-2</t>
+          <t>3-3-3-3-3-3-3</t>
         </is>
       </c>
       <c r="BB24" s="3" t="n">
@@ -12314,7 +14292,7 @@
         <v>100</v>
       </c>
       <c r="BD24" s="3" t="n">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="BE24" s="4" t="inlineStr">
         <is>
@@ -12329,7 +14307,7 @@
       </c>
       <c r="BH24" s="4" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="BI24" s="4" t="inlineStr">
@@ -12338,135 +14316,129 @@
         </is>
       </c>
       <c r="BJ24" s="3" t="n">
-        <v>3.59</v>
+        <v>3.17</v>
       </c>
       <c r="BK24" s="3" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" s="3" t="n">
-        <v>0.1972</v>
+        <v>0.1923</v>
       </c>
       <c r="BM24" s="3" t="n">
-        <v>0.0348</v>
+        <v>0.0308</v>
       </c>
       <c r="BN24" s="3" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="BO24" s="3" t="n">
-        <v>4.62</v>
+        <v>3.61</v>
       </c>
       <c r="BP24" s="3" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="BQ24" s="3" t="n">
-        <v>0.2211</v>
+        <v>0.2176</v>
       </c>
       <c r="BR24" s="3" t="n">
-        <v>0.0307</v>
+        <v>0.0254</v>
       </c>
       <c r="BS24" s="4" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BT24" s="3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="BU24" s="3" t="n">
-        <v>1.055</v>
-      </c>
-      <c r="BV24" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="BW24" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX24" s="3" t="n">
-        <v>223</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BV24" s="4" t="n"/>
+      <c r="BW24" s="4" t="n"/>
+      <c r="BX24" s="4" t="n"/>
       <c r="BY24" s="4" t="n"/>
       <c r="BZ24" s="4" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>Indoor/retractable neutral</t>
         </is>
       </c>
       <c r="CA24" s="3" t="n">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="CB24" s="3" t="n">
-        <v>283</v>
+        <v>355</v>
       </c>
       <c r="CC24" s="3" t="n">
-        <v>0.237</v>
+        <v>0.279</v>
       </c>
       <c r="CD24" s="3" t="n">
-        <v>0.39</v>
+        <v>0.372</v>
       </c>
       <c r="CE24" s="3" t="n">
-        <v>0.473</v>
+        <v>0.555</v>
       </c>
       <c r="CF24" s="3" t="n">
-        <v>0.863</v>
+        <v>0.927</v>
       </c>
       <c r="CG24" s="3" t="n">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="CH24" s="3" t="n">
-        <v>0.865</v>
+        <v>0.891</v>
       </c>
       <c r="CI24" s="3" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="CJ24" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CK24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CL24" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="CM24" s="3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CN24" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="CO24" s="3" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="CP24" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CQ24" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CR24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS</t>
+          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS</t>
         </is>
       </c>
       <c r="CS24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS|2026-06-16 @ Arizona Diamondbacks: 23 FS|2026-06-15 @ Arizona Diamondbacks: 21 FS|2026-06-14 vs Tampa Bay Rays: 5 FS|2026-06-13 vs Tampa Bay Rays: 8 FS|2026-06-12 vs Tampa Bay Rays: 9 FS</t>
+          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS|2026-07-07 vs New York Yankees: 0 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 2 FS|2026-07-04 @ Houston Astros: 26 FS|2026-07-03 @ Houston Astros: 14 FS</t>
         </is>
       </c>
       <c r="CT24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12 @ Minnesota Twins: 6 FS|2026-07-11 @ Minnesota Twins: 10 FS|2026-07-09 @ Texas Rangers: 4 FS|2026-07-08 @ Texas Rangers: 20 FS|2026-06-17 @ Arizona Diamondbacks: 5 FS|2026-06-16 @ Arizona Diamondbacks: 23 FS|2026-06-15 @ Arizona Diamondbacks: 21 FS|2026-06-14 vs Tampa Bay Rays: 5 FS|2026-06-13 vs Tampa Bay Rays: 8 FS|2026-06-12 vs Tampa Bay Rays: 9 FS|2026-06-10 vs Houston Astros: 21 FS|2026-06-09 vs Houston Astros: 9 FS|2026-06-08 vs Houston Astros: 2 FS|2026-06-07 @ Los Angeles Dodgers: 0 FS|2026-06-06 @ Los Angeles Dodgers: 0 FS</t>
+          <t>2026-07-12 vs Seattle Mariners: 2 FS|2026-07-11 vs Seattle Mariners: 16 FS|2026-07-10 vs Seattle Mariners: 25 FS|2026-07-09 vs New York Yankees: 16 FS|2026-07-08 vs New York Yankees: 0 FS|2026-07-07 vs New York Yankees: 0 FS|2026-07-06 vs New York Yankees: 0 FS|2026-07-05 @ Houston Astros: 2 FS|2026-07-04 @ Houston Astros: 26 FS|2026-07-03 @ Houston Astros: 14 FS|2026-07-02 @ Kansas City Royals: 0 FS|2026-07-01 @ Kansas City Royals: 16 FS|2026-06-30 @ Kansas City Royals: 21 FS|2026-06-28 vs Arizona Diamondbacks: 24 FS|2026-06-27 vs Arizona Diamondbacks: 14 FS</t>
         </is>
       </c>
       <c r="CU24" s="3" t="n">
         <v>15</v>
       </c>
       <c r="CV24" s="3" t="n">
-        <v>12.71</v>
+        <v>8.43</v>
       </c>
       <c r="CW24" s="3" t="n">
-        <v>10.21</v>
+        <v>11.57</v>
       </c>
       <c r="CX24" s="3" t="n">
-        <v>0.254</v>
+        <v>0.245</v>
       </c>
       <c r="CY24" s="4" t="inlineStr">
         <is>
@@ -12474,46 +14446,46 @@
         </is>
       </c>
       <c r="CZ24" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>11.27</v>
       </c>
       <c r="DA24" s="3" t="n">
-        <v>2.134</v>
+        <v>2.656</v>
       </c>
       <c r="DB24" s="3" t="n">
-        <v>0.2239</v>
+        <v>0.2131</v>
       </c>
       <c r="DC24" s="3" t="n">
-        <v>0.1045</v>
+        <v>0.1475</v>
       </c>
       <c r="DD24" s="3" t="n">
-        <v>0.0597</v>
+        <v>0.1148</v>
       </c>
       <c r="DE24" s="3" t="n">
-        <v>0.1045</v>
+        <v>0.1148</v>
       </c>
       <c r="DF24" s="3" t="n">
-        <v>0.0299</v>
+        <v>0.0328</v>
       </c>
       <c r="DG24" s="3" t="n">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="DH24" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>88.03</v>
       </c>
       <c r="DI24" s="3" t="n">
-        <v>24.62</v>
+        <v>41</v>
       </c>
       <c r="DJ24" s="3" t="n">
-        <v>2.51</v>
+        <v>3.45</v>
       </c>
       <c r="DK24" s="3" t="n">
-        <v>30.15</v>
+        <v>27.59</v>
       </c>
       <c r="DL24" s="3" t="n">
-        <v>0.456</v>
+        <v>0.433</v>
       </c>
       <c r="DM24" s="3" t="n">
-        <v>0.9715</v>
+        <v>1.0756</v>
       </c>
       <c r="DN24" s="3" t="n">
         <v>1</v>
@@ -12525,10 +14497,10 @@
         <v>1</v>
       </c>
       <c r="DQ24" s="3" t="n">
-        <v>1.058</v>
+        <v>1.0826</v>
       </c>
       <c r="DR24" s="3" t="n">
-        <v>431</v>
+        <v>620</v>
       </c>
       <c r="DS24" s="4" t="inlineStr">
         <is>
@@ -12536,43 +14508,43 @@
         </is>
       </c>
       <c r="DT24" s="3" t="n">
-        <v>0.1061</v>
+        <v>0.1131</v>
       </c>
       <c r="DU24" s="3" t="n">
-        <v>0.0395</v>
+        <v>0.0364</v>
       </c>
       <c r="DV24" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.0021</v>
       </c>
       <c r="DW24" s="3" t="n">
-        <v>0.0473</v>
+        <v>0.0599</v>
       </c>
       <c r="DX24" s="3" t="n">
-        <v>0.1504</v>
+        <v>0.0823</v>
       </c>
       <c r="DY24" s="3" t="n">
-        <v>0.0127</v>
+        <v>0.0064</v>
       </c>
       <c r="DZ24" s="3" t="n">
-        <v>0.2484</v>
+        <v>0.2081</v>
       </c>
       <c r="EA24" s="3" t="n">
-        <v>0.3667</v>
+        <v>0.5238</v>
       </c>
       <c r="EB24" s="3" t="n">
-        <v>0.3556</v>
+        <v>0.2518</v>
       </c>
       <c r="EC24" s="3" t="n">
-        <v>0.2778</v>
+        <v>0.2244</v>
       </c>
       <c r="ED24" s="3" t="n">
-        <v>0.1368</v>
+        <v>0.1242</v>
       </c>
       <c r="EE24" s="3" t="n">
-        <v>0.1086</v>
+        <v>0.1494</v>
       </c>
       <c r="EF24" s="3" t="n">
-        <v>0.0144</v>
+        <v>0.0107</v>
       </c>
       <c r="EG24" s="3" t="n">
         <v>1</v>
@@ -12581,33 +14553,115 @@
         <v>5</v>
       </c>
       <c r="EI24" s="3" t="n">
-        <v>7.69</v>
+        <v>7.97</v>
       </c>
       <c r="EJ24" s="3" t="n">
         <v>2</v>
       </c>
       <c r="EK24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="EL24" s="3" t="n">
         <v>19</v>
       </c>
       <c r="EM24" s="3" t="n">
-        <v>4.39</v>
+        <v>4.16</v>
       </c>
       <c r="EN24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="EO24" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP24" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP24" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="EQ24" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="ER24" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="ES24" s="3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="ET24" s="3" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="EU24" s="3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="EV24" s="3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="EW24" s="3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="EX24" s="3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="EY24" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="EZ24" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="FA24" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="FB24" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="FC24" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="FD24" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="FE24" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="FF24" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="FG24" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FH24" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="FI24" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="FJ24" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="FK24" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="FL24" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="FM24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="FN24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="FO24" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FP24" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FQ24" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -12655,7 +14709,7 @@
         <v>7.92</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10.56</v>
+        <v>10.57</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>5.2</v>
@@ -12697,34 +14751,34 @@
         <v>74.40000000000001</v>
       </c>
       <c r="W25" s="5" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="Z25" s="5" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="AA25" s="6" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="AC25" s="7" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="AD25" s="7" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="AE25" s="7" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AF25" s="7" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="AG25" s="7" t="n">
         <v>41.1</v>
@@ -12733,37 +14787,37 @@
         <v>41.1</v>
       </c>
       <c r="AI25" s="8" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="AJ25" s="8" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="AK25" s="8" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AL25" s="8" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AM25" s="8" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="AN25" s="8" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="AO25" s="8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="AP25" s="8" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="AQ25" s="8" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="AR25" s="8" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="AS25" s="3" t="n">
-        <v>220.95</v>
+        <v>221.06</v>
       </c>
       <c r="AT25" s="4" t="inlineStr">
         <is>
@@ -13065,7 +15119,7 @@
         <v>9</v>
       </c>
       <c r="EI25" s="3" t="n">
-        <v>8.34</v>
+        <v>8.35</v>
       </c>
       <c r="EJ25" s="3" t="n">
         <v>4</v>
@@ -13084,14 +15138,96 @@
       </c>
       <c r="EO25" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP25" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP25" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="EQ25" s="3" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="ER25" s="3" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="ES25" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="ET25" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="EU25" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="EV25" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="EW25" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="EX25" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="EY25" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="EZ25" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="FA25" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="FB25" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="FC25" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="FD25" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="FE25" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="FF25" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="FG25" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FH25" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="FI25" s="3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="FJ25" s="3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="FK25" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="FL25" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="FM25" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FN25" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="FO25" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="FP25" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="FQ25" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+      <c r="FR25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -13139,7 +15275,7 @@
         <v>9.59</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>12.8</v>
@@ -13169,58 +15305,58 @@
         <v>71</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="V26" s="7" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="X26" s="7" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="Y26" s="7" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="Z26" s="7" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="AA26" s="8" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="AC26" s="8" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="AD26" s="8" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="AF26" s="8" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="AG26" s="8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AH26" s="8" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="AI26" s="8" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="AJ26" s="8" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="AK26" s="8" t="n">
         <v>24.2</v>
@@ -13229,25 +15365,25 @@
         <v>24.2</v>
       </c>
       <c r="AM26" s="8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AN26" s="8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AO26" s="8" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AP26" s="8" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AQ26" s="8" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AR26" s="8" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AS26" s="3" t="n">
-        <v>220.6</v>
+        <v>220.41</v>
       </c>
       <c r="AT26" s="4" t="inlineStr">
         <is>
@@ -13555,7 +15691,7 @@
         <v>5</v>
       </c>
       <c r="EI26" s="3" t="n">
-        <v>7.81</v>
+        <v>7.79</v>
       </c>
       <c r="EJ26" s="3" t="n">
         <v>2</v>
@@ -13574,14 +15710,96 @@
       </c>
       <c r="EO26" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP26" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP26" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="EQ26" s="3" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="ER26" s="3" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="ES26" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="ET26" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="EU26" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="EV26" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="EW26" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="EX26" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="EY26" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="EZ26" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="FA26" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="FB26" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="FC26" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="FD26" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="FE26" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="FF26" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="FG26" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="FH26" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="FI26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="FJ26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="FK26" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FL26" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="FM26" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="FN26" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="FO26" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="FP26" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="FQ26" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -13629,7 +15847,7 @@
         <v>8.91</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>6</v>
@@ -13713,16 +15931,16 @@
         <v>20.6</v>
       </c>
       <c r="AK27" s="8" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AL27" s="8" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AM27" s="8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AN27" s="8" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AO27" s="8" t="n">
         <v>13</v>
@@ -13731,13 +15949,13 @@
         <v>13</v>
       </c>
       <c r="AQ27" s="8" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="AR27" s="8" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="AS27" s="3" t="n">
-        <v>220.01</v>
+        <v>220.08</v>
       </c>
       <c r="AT27" s="4" t="inlineStr">
         <is>
@@ -14039,7 +16257,7 @@
         <v>5</v>
       </c>
       <c r="EI27" s="3" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
       <c r="EJ27" s="3" t="n">
         <v>2</v>
@@ -14058,14 +16276,96 @@
       </c>
       <c r="EO27" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP27" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP27" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="EQ27" s="3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="ER27" s="3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="ES27" s="3" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="ET27" s="3" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="EU27" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="EV27" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="EW27" s="3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="EX27" s="3" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="EY27" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="EZ27" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="FA27" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="FB27" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="FC27" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="FD27" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="FE27" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FF27" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FG27" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="FH27" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="FI27" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="FJ27" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="FK27" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="FL27" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="FM27" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="FN27" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="FO27" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="FP27" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="FQ27" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -14548,14 +16848,96 @@
       </c>
       <c r="EO28" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP28" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP28" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="EQ28" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="ER28" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="ES28" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="ET28" s="3" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="EU28" s="3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="EV28" s="3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="EW28" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="EX28" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="EY28" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="EZ28" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="FA28" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="FB28" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="FC28" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="FD28" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="FE28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="FF28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="FG28" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="FH28" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="FI28" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="FJ28" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="FK28" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FL28" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FM28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="FN28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="FO28" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="FP28" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="FQ28" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -14630,7 +17012,7 @@
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="S29" s="6" t="n">
         <v>57.6</v>
@@ -14657,16 +17039,16 @@
         <v>40.2</v>
       </c>
       <c r="AA29" s="8" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="AD29" s="8" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="AE29" s="8" t="n">
         <v>26.3</v>
@@ -14681,16 +17063,16 @@
         <v>22.9</v>
       </c>
       <c r="AI29" s="8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AJ29" s="8" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AK29" s="8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AL29" s="8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AM29" s="8" t="n">
         <v>18.7</v>
@@ -14711,7 +17093,7 @@
         <v>14.4</v>
       </c>
       <c r="AS29" s="3" t="n">
-        <v>216.41</v>
+        <v>216.39</v>
       </c>
       <c r="AT29" s="4" t="inlineStr">
         <is>
@@ -15019,7 +17401,7 @@
         <v>5</v>
       </c>
       <c r="EI29" s="3" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="EJ29" s="3" t="n">
         <v>2</v>
@@ -15038,14 +17420,96 @@
       </c>
       <c r="EO29" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP29" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP29" s="3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="EQ29" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="ER29" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="ES29" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="ET29" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="EU29" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="EV29" s="3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="EW29" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="EX29" s="3" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="EY29" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="EZ29" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="FA29" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="FB29" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="FC29" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="FD29" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="FE29" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FF29" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FG29" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="FH29" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="FI29" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="FJ29" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="FK29" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FL29" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="FM29" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="FN29" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="FO29" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="FP29" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="FQ29" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -15183,10 +17647,10 @@
         <v>24.5</v>
       </c>
       <c r="AM30" s="8" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AN30" s="8" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AO30" s="8" t="n">
         <v>19.1</v>
@@ -15522,14 +17986,96 @@
       </c>
       <c r="EO30" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP30" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP30" s="3" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="EQ30" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="ER30" s="3" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="ES30" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="ET30" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="EU30" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="EV30" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="EW30" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="EX30" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="EY30" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="EZ30" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="FA30" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="FB30" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="FC30" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="FD30" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="FE30" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="FF30" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="FG30" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="FH30" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="FI30" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FJ30" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="FK30" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="FL30" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="FM30" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="FN30" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="FO30" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="FP30" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="FQ30" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -15577,7 +18123,7 @@
         <v>8.85</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>12.4</v>
@@ -15613,10 +18159,10 @@
         <v>68</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="W31" s="6" t="n">
         <v>52.5</v>
@@ -15625,22 +18171,22 @@
         <v>52.5</v>
       </c>
       <c r="Y31" s="7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="Z31" s="7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="AA31" s="7" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="AB31" s="7" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="AC31" s="8" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AD31" s="8" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="AE31" s="8" t="n">
         <v>32.6</v>
@@ -15649,43 +18195,43 @@
         <v>32.6</v>
       </c>
       <c r="AG31" s="8" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="AH31" s="8" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="AI31" s="8" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="AJ31" s="8" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="AK31" s="8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AL31" s="8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AM31" s="8" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AN31" s="8" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AO31" s="8" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="AP31" s="8" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ31" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="AR31" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="AS31" s="3" t="n">
-        <v>214.97</v>
+        <v>214.87</v>
       </c>
       <c r="AT31" s="4" t="inlineStr">
         <is>
@@ -15987,7 +18533,7 @@
         <v>6</v>
       </c>
       <c r="EI31" s="3" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
       <c r="EJ31" s="3" t="n">
         <v>3</v>
@@ -16006,17 +18552,99 @@
       </c>
       <c r="EO31" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
-        </is>
-      </c>
-      <c r="EP31" s="4" t="inlineStr">
+          <t>Raw (calibration off)</t>
+        </is>
+      </c>
+      <c r="EP31" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="EQ31" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="ER31" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="ES31" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="ET31" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="EU31" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="EV31" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="EW31" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="EX31" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="EY31" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="EZ31" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="FA31" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="FB31" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="FC31" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="FD31" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="FE31" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="FF31" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="FG31" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="FH31" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="FI31" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FJ31" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="FK31" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="FL31" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="FM31" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="FN31" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="FO31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="FP31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="FQ31" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="FR31" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:EP31"/>
+  <autoFilter ref="A1:FR31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_12.xlsx
+++ b/PRIZEPICKS_HITTER_AI_V4_TOP30_2026_07_12.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitter Model" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hitter Model'!$A$1:$GB$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hitter Model'!$A$1:$HC$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GB31"/>
+  <dimension ref="A1:HC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,33 @@
     <col width="13" customWidth="1" min="182" max="182"/>
     <col width="13" customWidth="1" min="183" max="183"/>
     <col width="12" customWidth="1" min="184" max="184"/>
+    <col width="12" customWidth="1" min="185" max="185"/>
+    <col width="12" customWidth="1" min="186" max="186"/>
+    <col width="12" customWidth="1" min="187" max="187"/>
+    <col width="12" customWidth="1" min="188" max="188"/>
+    <col width="12" customWidth="1" min="189" max="189"/>
+    <col width="12" customWidth="1" min="190" max="190"/>
+    <col width="12" customWidth="1" min="191" max="191"/>
+    <col width="12" customWidth="1" min="192" max="192"/>
+    <col width="12" customWidth="1" min="193" max="193"/>
+    <col width="12" customWidth="1" min="194" max="194"/>
+    <col width="12" customWidth="1" min="195" max="195"/>
+    <col width="12" customWidth="1" min="196" max="196"/>
+    <col width="12" customWidth="1" min="197" max="197"/>
+    <col width="12" customWidth="1" min="198" max="198"/>
+    <col width="12" customWidth="1" min="199" max="199"/>
+    <col width="12" customWidth="1" min="200" max="200"/>
+    <col width="12" customWidth="1" min="201" max="201"/>
+    <col width="12" customWidth="1" min="202" max="202"/>
+    <col width="12" customWidth="1" min="203" max="203"/>
+    <col width="12" customWidth="1" min="204" max="204"/>
+    <col width="12" customWidth="1" min="205" max="205"/>
+    <col width="12" customWidth="1" min="206" max="206"/>
+    <col width="12" customWidth="1" min="207" max="207"/>
+    <col width="12" customWidth="1" min="208" max="208"/>
+    <col width="12" customWidth="1" min="209" max="209"/>
+    <col width="12" customWidth="1" min="210" max="210"/>
+    <col width="12" customWidth="1" min="211" max="211"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1617,6 +1644,141 @@
       </c>
       <c r="GB1" s="2" t="inlineStr">
         <is>
+          <t>Floor Uplift 2.5 FS</t>
+        </is>
+      </c>
+      <c r="GC1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 3.0 FS</t>
+        </is>
+      </c>
+      <c r="GD1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 3.5 FS</t>
+        </is>
+      </c>
+      <c r="GE1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 4.0 FS</t>
+        </is>
+      </c>
+      <c r="GF1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 4.5 FS</t>
+        </is>
+      </c>
+      <c r="GG1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 5.0 FS</t>
+        </is>
+      </c>
+      <c r="GH1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 5.5 FS</t>
+        </is>
+      </c>
+      <c r="GI1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 6.0 FS</t>
+        </is>
+      </c>
+      <c r="GJ1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 6.5 FS</t>
+        </is>
+      </c>
+      <c r="GK1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 7.0 FS</t>
+        </is>
+      </c>
+      <c r="GL1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 7.5 FS</t>
+        </is>
+      </c>
+      <c r="GM1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 8.0 FS</t>
+        </is>
+      </c>
+      <c r="GN1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 8.5 FS</t>
+        </is>
+      </c>
+      <c r="GO1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 9.0 FS</t>
+        </is>
+      </c>
+      <c r="GP1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 9.5 FS</t>
+        </is>
+      </c>
+      <c r="GQ1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 10.0 FS</t>
+        </is>
+      </c>
+      <c r="GR1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 10.5 FS</t>
+        </is>
+      </c>
+      <c r="GS1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 11.0 FS</t>
+        </is>
+      </c>
+      <c r="GT1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 11.5 FS</t>
+        </is>
+      </c>
+      <c r="GU1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 12.0 FS</t>
+        </is>
+      </c>
+      <c r="GV1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 12.5 FS</t>
+        </is>
+      </c>
+      <c r="GW1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 13.0 FS</t>
+        </is>
+      </c>
+      <c r="GX1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 13.5 FS</t>
+        </is>
+      </c>
+      <c r="GY1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 14.0 FS</t>
+        </is>
+      </c>
+      <c r="GZ1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 14.5 FS</t>
+        </is>
+      </c>
+      <c r="HA1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 15.0 FS</t>
+        </is>
+      </c>
+      <c r="HB1" s="2" t="inlineStr">
+        <is>
+          <t>Floor Uplift 15.5 FS</t>
+        </is>
+      </c>
+      <c r="HC1" s="2" t="inlineStr">
+        <is>
           <t>Confidence</t>
         </is>
       </c>
@@ -1694,40 +1856,40 @@
         </is>
       </c>
       <c r="R2" s="5" t="n">
-        <v>85.3</v>
+        <v>91.2</v>
       </c>
       <c r="S2" s="5" t="n">
-        <v>79.7</v>
+        <v>87.7</v>
       </c>
       <c r="T2" s="5" t="n">
-        <v>79.7</v>
+        <v>87.2</v>
       </c>
       <c r="U2" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="W2" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="X2" s="5" t="n">
-        <v>67.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>63.5</v>
+        <v>67.5</v>
       </c>
       <c r="Z2" s="5" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="AA2" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="AB2" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="AC2" s="7" t="n">
-        <v>52</v>
+        <v>67</v>
+      </c>
+      <c r="AA2" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AB2" s="5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AC2" s="6" t="n">
+        <v>53</v>
       </c>
       <c r="AD2" s="7" t="n">
         <v>52</v>
@@ -1775,7 +1937,7 @@
         <v>29.4</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>299.26</v>
+        <v>299.98</v>
       </c>
       <c r="AT2" s="4" t="inlineStr">
         <is>
@@ -2221,7 +2383,88 @@
       <c r="GA2" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="GB2" s="4" t="inlineStr">
+      <c r="GB2" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="GC2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD2" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH2" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ2" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL2" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC2" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2300,40 +2543,40 @@
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>85.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>80.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>80.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>75.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>75.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="W3" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>63.5</v>
+        <v>67.5</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="AA3" s="6" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="AB3" s="7" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="AC3" s="7" t="n">
-        <v>51.9</v>
+        <v>67</v>
+      </c>
+      <c r="AA3" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AB3" s="5" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="AC3" s="6" t="n">
+        <v>52.9</v>
       </c>
       <c r="AD3" s="7" t="n">
         <v>51.9</v>
@@ -2381,7 +2624,7 @@
         <v>27.4</v>
       </c>
       <c r="AS3" s="3" t="n">
-        <v>283.86</v>
+        <v>284.58</v>
       </c>
       <c r="AT3" s="4" t="inlineStr">
         <is>
@@ -2827,7 +3070,88 @@
       <c r="GA3" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="GB3" s="4" t="inlineStr">
+      <c r="GB3" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="GC3" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="GD3" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="GE3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH3" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ3" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL3" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC3" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2906,40 +3230,40 @@
         </is>
       </c>
       <c r="R4" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>77.7</v>
+        <v>85.7</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>77.7</v>
+        <v>85.2</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>73.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>73.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="X4" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>61.5</v>
+        <v>65.5</v>
       </c>
       <c r="Z4" s="5" t="n">
-        <v>61.5</v>
+        <v>65</v>
       </c>
       <c r="AA4" s="6" t="n">
-        <v>54.5</v>
+        <v>57.5</v>
       </c>
       <c r="AB4" s="7" t="n">
-        <v>54.5</v>
+        <v>57</v>
       </c>
       <c r="AC4" s="7" t="n">
-        <v>49.7</v>
+        <v>50.7</v>
       </c>
       <c r="AD4" s="7" t="n">
         <v>49.7</v>
@@ -2987,7 +3311,7 @@
         <v>25.7</v>
       </c>
       <c r="AS4" s="3" t="n">
-        <v>279.93</v>
+        <v>280.65</v>
       </c>
       <c r="AT4" s="4" t="inlineStr">
         <is>
@@ -3427,7 +3751,88 @@
       <c r="GA4" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="GB4" s="4" t="inlineStr">
+      <c r="GB4" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="GC4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD4" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH4" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ4" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL4" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC4" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3506,40 +3911,40 @@
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>82.5</v>
+        <v>89.5</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>76.2</v>
+        <v>84.2</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>76.2</v>
+        <v>83.7</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>71.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>63</v>
+        <v>67.5</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>59.3</v>
+        <v>63.3</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>59.3</v>
+        <v>62.8</v>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>52.6</v>
+        <v>55.6</v>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>52.6</v>
+        <v>55.1</v>
       </c>
       <c r="AC5" s="7" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="AD5" s="7" t="n">
         <v>48.8</v>
@@ -3587,7 +3992,7 @@
         <v>29</v>
       </c>
       <c r="AS5" s="3" t="n">
-        <v>272.38</v>
+        <v>273.1</v>
       </c>
       <c r="AT5" s="4" t="inlineStr">
         <is>
@@ -4027,7 +4432,88 @@
       <c r="GA5" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="GB5" s="4" t="inlineStr">
+      <c r="GB5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GC5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD5" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH5" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ5" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL5" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC5" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4106,40 +4592,40 @@
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>74.5</v>
+        <v>82.5</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>52.4</v>
+        <v>57.4</v>
       </c>
       <c r="X6" s="7" t="n">
-        <v>52.4</v>
+        <v>56.9</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>49.8</v>
+        <v>53.8</v>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>49.8</v>
+        <v>53.3</v>
       </c>
       <c r="AA6" s="7" t="n">
-        <v>43.1</v>
+        <v>46.1</v>
       </c>
       <c r="AB6" s="7" t="n">
-        <v>43.1</v>
+        <v>45.6</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AD6" s="7" t="n">
         <v>40</v>
@@ -4187,7 +4673,7 @@
         <v>23.2</v>
       </c>
       <c r="AS6" s="3" t="n">
-        <v>263.52</v>
+        <v>264.24</v>
       </c>
       <c r="AT6" s="4" t="inlineStr">
         <is>
@@ -4633,7 +5119,88 @@
       <c r="GA6" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="GB6" s="4" t="inlineStr">
+      <c r="GB6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD6" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ6" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL6" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC6" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4712,40 +5279,40 @@
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>86.2</v>
+        <v>91.7</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>78.3</v>
+        <v>86.3</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>78.3</v>
+        <v>85.8</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="AA7" s="6" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="AB7" s="7" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="AC7" s="7" t="n">
-        <v>50.2</v>
+        <v>66.5</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AB7" s="5" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="AC7" s="6" t="n">
+        <v>51.2</v>
       </c>
       <c r="AD7" s="7" t="n">
         <v>50.2</v>
@@ -4793,7 +5360,7 @@
         <v>24.9</v>
       </c>
       <c r="AS7" s="3" t="n">
-        <v>263.19</v>
+        <v>263.91</v>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
@@ -5239,7 +5806,88 @@
       <c r="GA7" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="GB7" s="4" t="inlineStr">
+      <c r="GB7" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="GC7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD7" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH7" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ7" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL7" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC7" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5318,40 +5966,40 @@
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>83.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>75.8</v>
+        <v>83.8</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>75.8</v>
+        <v>83.3</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>71.7</v>
+        <v>78.7</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>71.7</v>
+        <v>77.7</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>62.8</v>
+        <v>67.8</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>62.8</v>
+        <v>67.3</v>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>59.4</v>
+        <v>63.4</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>59.4</v>
+        <v>62.9</v>
       </c>
       <c r="AA8" s="6" t="n">
-        <v>52.1</v>
+        <v>55.1</v>
       </c>
       <c r="AB8" s="7" t="n">
-        <v>52.1</v>
+        <v>54.6</v>
       </c>
       <c r="AC8" s="7" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="AD8" s="7" t="n">
         <v>47.5</v>
@@ -5399,7 +6047,7 @@
         <v>24.7</v>
       </c>
       <c r="AS8" s="3" t="n">
-        <v>262.31</v>
+        <v>263.03</v>
       </c>
       <c r="AT8" s="4" t="inlineStr">
         <is>
@@ -5845,7 +6493,88 @@
       <c r="GA8" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="GB8" s="4" t="inlineStr">
+      <c r="GB8" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="GC8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD8" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH8" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ8" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL8" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC8" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5924,40 +6653,40 @@
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>78.8</v>
+        <v>86.8</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>66.5</v>
+        <v>73.5</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="X9" s="7" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="Y9" s="7" t="n">
-        <v>53.7</v>
+        <v>72.5</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>57.7</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>53.7</v>
+        <v>57.2</v>
       </c>
       <c r="AA9" s="7" t="n">
-        <v>47.3</v>
+        <v>50.3</v>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>47.3</v>
+        <v>49.8</v>
       </c>
       <c r="AC9" s="7" t="n">
-        <v>42.9</v>
+        <v>43.9</v>
       </c>
       <c r="AD9" s="7" t="n">
         <v>42.9</v>
@@ -6005,7 +6734,7 @@
         <v>23.9</v>
       </c>
       <c r="AS9" s="3" t="n">
-        <v>260.64</v>
+        <v>261.36</v>
       </c>
       <c r="AT9" s="4" t="inlineStr">
         <is>
@@ -6451,7 +7180,88 @@
       <c r="GA9" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="GB9" s="4" t="inlineStr">
+      <c r="GB9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD9" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH9" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ9" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL9" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC9" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6530,40 +7340,40 @@
         </is>
       </c>
       <c r="R10" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>79.3</v>
+        <v>87.3</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>79.3</v>
+        <v>86.8</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>74.2</v>
+        <v>81.2</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>74.2</v>
+        <v>80.2</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="X10" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>62.5</v>
+        <v>66.5</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AA10" s="6" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="AB10" s="7" t="n">
-        <v>55.2</v>
+        <v>66</v>
+      </c>
+      <c r="AA10" s="5" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="AB10" s="6" t="n">
+        <v>57.7</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>51.1</v>
+        <v>52.1</v>
       </c>
       <c r="AD10" s="7" t="n">
         <v>51.1</v>
@@ -6611,7 +7421,7 @@
         <v>28</v>
       </c>
       <c r="AS10" s="3" t="n">
-        <v>260.46</v>
+        <v>261.18</v>
       </c>
       <c r="AT10" s="4" t="inlineStr">
         <is>
@@ -7051,7 +7861,88 @@
       <c r="GA10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="GB10" s="4" t="inlineStr">
+      <c r="GB10" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="GC10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD10" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH10" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ10" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL10" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC10" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7130,40 +8021,40 @@
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>83.7</v>
+        <v>90.2</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>76.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>72.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>63.2</v>
+        <v>68.2</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>63.2</v>
+        <v>67.7</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>59.8</v>
+        <v>63.8</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>59.8</v>
+        <v>63.3</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>51.7</v>
+        <v>54.7</v>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>51.7</v>
+        <v>54.2</v>
       </c>
       <c r="AC11" s="7" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="AD11" s="7" t="n">
         <v>47.4</v>
@@ -7211,7 +8102,7 @@
         <v>23.1</v>
       </c>
       <c r="AS11" s="3" t="n">
-        <v>249.41</v>
+        <v>250.13</v>
       </c>
       <c r="AT11" s="4" t="inlineStr">
         <is>
@@ -7651,7 +8542,88 @@
       <c r="GA11" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="GB11" s="4" t="inlineStr">
+      <c r="GB11" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="GC11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD11" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH11" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ11" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC11" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -7730,40 +8702,40 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>65.7</v>
+        <v>73.7</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>65.7</v>
+        <v>73.2</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>60.8</v>
+        <v>67.8</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>60.8</v>
+        <v>66.8</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>51.3</v>
+        <v>56.3</v>
       </c>
       <c r="X12" s="7" t="n">
-        <v>51.3</v>
+        <v>55.8</v>
       </c>
       <c r="Y12" s="7" t="n">
-        <v>47.9</v>
+        <v>51.9</v>
       </c>
       <c r="Z12" s="7" t="n">
-        <v>47.9</v>
+        <v>51.4</v>
       </c>
       <c r="AA12" s="7" t="n">
-        <v>41.1</v>
+        <v>44.1</v>
       </c>
       <c r="AB12" s="7" t="n">
-        <v>41.1</v>
+        <v>43.6</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>37.4</v>
+        <v>38.4</v>
       </c>
       <c r="AD12" s="8" t="n">
         <v>37.4</v>
@@ -7811,7 +8783,7 @@
         <v>21.3</v>
       </c>
       <c r="AS12" s="3" t="n">
-        <v>247.32</v>
+        <v>248.04</v>
       </c>
       <c r="AT12" s="4" t="inlineStr">
         <is>
@@ -8257,7 +9229,88 @@
       <c r="GA12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="GB12" s="4" t="inlineStr">
+      <c r="GB12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD12" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH12" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ12" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC12" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8336,40 +9389,40 @@
         </is>
       </c>
       <c r="R13" s="5" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="T13" s="5" t="n">
         <v>79.7</v>
       </c>
-      <c r="S13" s="5" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>72.2</v>
-      </c>
       <c r="U13" s="5" t="n">
-        <v>67.3</v>
+        <v>74.3</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>67.3</v>
+        <v>73.3</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y13" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z13" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA13" s="7" t="n">
-        <v>47.5</v>
+        <v>62.5</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AA13" s="6" t="n">
+        <v>50.5</v>
       </c>
       <c r="AB13" s="7" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="AC13" s="7" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
       <c r="AD13" s="7" t="n">
         <v>43.7</v>
@@ -8417,7 +9470,7 @@
         <v>22.9</v>
       </c>
       <c r="AS13" s="3" t="n">
-        <v>246.44</v>
+        <v>247.16</v>
       </c>
       <c r="AT13" s="4" t="inlineStr">
         <is>
@@ -8863,9 +9916,90 @@
       <c r="GA13" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="GB13" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="GB13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD13" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH13" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ13" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC13" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -8942,40 +10076,40 @@
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>76.8</v>
+        <v>84.8</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="X14" s="7" t="n">
-        <v>53.3</v>
+        <v>69</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="X14" s="6" t="n">
+        <v>57.8</v>
       </c>
       <c r="Y14" s="7" t="n">
-        <v>49.4</v>
+        <v>53.4</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>49.4</v>
+        <v>52.9</v>
       </c>
       <c r="AA14" s="7" t="n">
-        <v>42.6</v>
+        <v>45.6</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>42.6</v>
+        <v>45.1</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>38.7</v>
+        <v>39.7</v>
       </c>
       <c r="AD14" s="8" t="n">
         <v>38.7</v>
@@ -9023,7 +10157,7 @@
         <v>21.8</v>
       </c>
       <c r="AS14" s="3" t="n">
-        <v>246.38</v>
+        <v>247.1</v>
       </c>
       <c r="AT14" s="4" t="inlineStr">
         <is>
@@ -9463,7 +10597,88 @@
       <c r="GA14" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="GB14" s="4" t="inlineStr">
+      <c r="GB14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD14" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE14" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH14" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ14" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL14" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC14" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9542,40 +10757,40 @@
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>83.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>76.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>76.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="W15" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Y15" s="5" t="n">
         <v>62.9</v>
       </c>
-      <c r="X15" s="5" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="Y15" s="5" t="n">
-        <v>58.9</v>
-      </c>
       <c r="Z15" s="5" t="n">
-        <v>58.9</v>
+        <v>62.4</v>
       </c>
       <c r="AA15" s="6" t="n">
-        <v>50.5</v>
+        <v>53.5</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>50.5</v>
+        <v>53</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="AD15" s="7" t="n">
         <v>45.9</v>
@@ -9623,7 +10838,7 @@
         <v>19.2</v>
       </c>
       <c r="AS15" s="3" t="n">
-        <v>243.08</v>
+        <v>243.8</v>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
@@ -10063,7 +11278,88 @@
       <c r="GA15" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="GB15" s="4" t="inlineStr">
+      <c r="GB15" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="GC15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD15" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH15" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ15" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL15" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC15" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -10142,40 +11438,40 @@
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>77.8</v>
+        <v>85.8</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>70.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="U16" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="W16" s="6" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="X16" s="7" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="Y16" s="7" t="n">
-        <v>52.2</v>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>56.2</v>
       </c>
       <c r="Z16" s="7" t="n">
-        <v>52.2</v>
+        <v>55.7</v>
       </c>
       <c r="AA16" s="7" t="n">
-        <v>44.7</v>
+        <v>47.7</v>
       </c>
       <c r="AB16" s="7" t="n">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>40.3</v>
+        <v>41.3</v>
       </c>
       <c r="AD16" s="7" t="n">
         <v>40.3</v>
@@ -10223,7 +11519,7 @@
         <v>20.5</v>
       </c>
       <c r="AS16" s="3" t="n">
-        <v>237.91</v>
+        <v>238.63</v>
       </c>
       <c r="AT16" s="4" t="inlineStr">
         <is>
@@ -10669,7 +11965,88 @@
       <c r="GA16" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="GB16" s="4" t="inlineStr">
+      <c r="GB16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD16" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH16" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ16" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL16" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC16" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10748,40 +12125,40 @@
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>71.5</v>
+        <v>78.5</v>
       </c>
       <c r="V17" s="5" t="n">
-        <v>71.5</v>
+        <v>77.5</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>60.5</v>
+        <v>65.5</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="Y17" s="6" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="Z17" s="7" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="AA17" s="7" t="n">
-        <v>49</v>
+        <v>65</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AA17" s="6" t="n">
+        <v>52</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>49</v>
+        <v>51.5</v>
       </c>
       <c r="AC17" s="7" t="n">
-        <v>42.3</v>
+        <v>43.3</v>
       </c>
       <c r="AD17" s="7" t="n">
         <v>42.3</v>
@@ -10829,7 +12206,7 @@
         <v>14.8</v>
       </c>
       <c r="AS17" s="3" t="n">
-        <v>236.72</v>
+        <v>237.44</v>
       </c>
       <c r="AT17" s="4" t="inlineStr">
         <is>
@@ -11275,9 +12652,90 @@
       <c r="GA17" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="GB17" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="GB17" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="GC17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD17" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH17" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ17" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL17" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC17" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -11354,40 +12812,40 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>72.7</v>
+        <v>80.7</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>63.2</v>
+        <v>71.2</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>63.2</v>
+        <v>70.7</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>58.5</v>
+        <v>65.5</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>58.5</v>
+        <v>64.5</v>
       </c>
       <c r="W18" s="6" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="Z18" s="7" t="n">
         <v>48.9</v>
       </c>
-      <c r="X18" s="7" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="Y18" s="7" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="Z18" s="7" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="AA18" s="8" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="AB18" s="8" t="n">
-        <v>39.3</v>
+      <c r="AA18" s="7" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <v>41.8</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="AD18" s="8" t="n">
         <v>35.5</v>
@@ -11435,7 +12893,7 @@
         <v>19.5</v>
       </c>
       <c r="AS18" s="3" t="n">
-        <v>236.66</v>
+        <v>237.38</v>
       </c>
       <c r="AT18" s="4" t="inlineStr">
         <is>
@@ -11881,7 +13339,88 @@
       <c r="GA18" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="GB18" s="4" t="inlineStr">
+      <c r="GB18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD18" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH18" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ18" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL18" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC18" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11960,40 +13499,40 @@
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>72.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>70.2</v>
+        <v>77.2</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>70.2</v>
+        <v>76.2</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>59.5</v>
+        <v>64.5</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="Y19" s="6" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="Z19" s="7" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="AA19" s="7" t="n">
-        <v>49.7</v>
+        <v>64</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="AA19" s="6" t="n">
+        <v>52.7</v>
       </c>
       <c r="AB19" s="7" t="n">
-        <v>49.7</v>
+        <v>52.2</v>
       </c>
       <c r="AC19" s="7" t="n">
-        <v>44.1</v>
+        <v>45.1</v>
       </c>
       <c r="AD19" s="7" t="n">
         <v>44.1</v>
@@ -12041,7 +13580,7 @@
         <v>21.9</v>
       </c>
       <c r="AS19" s="3" t="n">
-        <v>236.28</v>
+        <v>237</v>
       </c>
       <c r="AT19" s="4" t="inlineStr">
         <is>
@@ -12487,9 +14026,90 @@
       <c r="GA19" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="GB19" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="GB19" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="GC19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD19" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH19" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ19" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC19" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -12566,40 +14186,40 @@
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>66.3</v>
+        <v>74.3</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>66.3</v>
+        <v>73.8</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>62.7</v>
+        <v>69.7</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>62.7</v>
+        <v>68.7</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>52.5</v>
+        <v>57.5</v>
       </c>
       <c r="X20" s="7" t="n">
-        <v>52.5</v>
+        <v>57</v>
       </c>
       <c r="Y20" s="7" t="n">
-        <v>49.4</v>
+        <v>53.4</v>
       </c>
       <c r="Z20" s="7" t="n">
-        <v>49.4</v>
+        <v>52.9</v>
       </c>
       <c r="AA20" s="7" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB20" s="7" t="n">
-        <v>43</v>
+        <v>45.5</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="AD20" s="8" t="n">
         <v>38.5</v>
@@ -12647,7 +14267,7 @@
         <v>18.6</v>
       </c>
       <c r="AS20" s="3" t="n">
-        <v>235.09</v>
+        <v>235.81</v>
       </c>
       <c r="AT20" s="4" t="inlineStr">
         <is>
@@ -13093,7 +14713,88 @@
       <c r="GA20" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="GB20" s="4" t="inlineStr">
+      <c r="GB20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD20" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH20" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ20" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL20" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC20" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13172,40 +14873,40 @@
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>78.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>72.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>65.5</v>
+        <v>72.5</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="X21" s="7" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="Y21" s="7" t="n">
-        <v>52.5</v>
+        <v>71.5</v>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>56.5</v>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>52.5</v>
+        <v>56</v>
       </c>
       <c r="AA21" s="7" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="AB21" s="7" t="n">
-        <v>44.5</v>
+        <v>47</v>
       </c>
       <c r="AC21" s="7" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="AD21" s="7" t="n">
         <v>41.1</v>
@@ -13253,7 +14954,7 @@
         <v>19.8</v>
       </c>
       <c r="AS21" s="3" t="n">
-        <v>234.12</v>
+        <v>234.84</v>
       </c>
       <c r="AT21" s="4" t="inlineStr">
         <is>
@@ -13699,7 +15400,88 @@
       <c r="GA21" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="GB21" s="4" t="inlineStr">
+      <c r="GB21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD21" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE21" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH21" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ21" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC21" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13778,40 +15560,40 @@
         </is>
       </c>
       <c r="R22" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>65.3</v>
+        <v>73.3</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>65.3</v>
+        <v>72.8</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>60.4</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>60.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>50.2</v>
+        <v>55.2</v>
       </c>
       <c r="X22" s="7" t="n">
-        <v>50.2</v>
+        <v>54.7</v>
       </c>
       <c r="Y22" s="7" t="n">
-        <v>47.3</v>
+        <v>51.3</v>
       </c>
       <c r="Z22" s="7" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="AA22" s="8" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="AB22" s="8" t="n">
-        <v>39.6</v>
+        <v>50.8</v>
+      </c>
+      <c r="AA22" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AB22" s="7" t="n">
+        <v>42.1</v>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>35.9</v>
+        <v>36.9</v>
       </c>
       <c r="AD22" s="8" t="n">
         <v>35.9</v>
@@ -13859,7 +15641,7 @@
         <v>18</v>
       </c>
       <c r="AS22" s="3" t="n">
-        <v>233.48</v>
+        <v>234.2</v>
       </c>
       <c r="AT22" s="4" t="inlineStr">
         <is>
@@ -14305,7 +16087,88 @@
       <c r="GA22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="GB22" s="4" t="inlineStr">
+      <c r="GB22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD22" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH22" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ22" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC22" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14384,40 +16247,40 @@
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>73.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>67.8</v>
+        <v>75.8</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>67.8</v>
+        <v>75.3</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>60.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>60.9</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>52.8</v>
+        <v>57.8</v>
       </c>
       <c r="X23" s="7" t="n">
-        <v>52.8</v>
+        <v>57.3</v>
       </c>
       <c r="Y23" s="7" t="n">
-        <v>48.5</v>
+        <v>52.5</v>
       </c>
       <c r="Z23" s="7" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="AA23" s="7" t="n">
-        <v>41.6</v>
+        <v>44.6</v>
       </c>
       <c r="AB23" s="7" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>38.2</v>
+        <v>39.2</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>38.2</v>
@@ -14465,7 +16328,7 @@
         <v>20.8</v>
       </c>
       <c r="AS23" s="3" t="n">
-        <v>231.86</v>
+        <v>232.58</v>
       </c>
       <c r="AT23" s="4" t="inlineStr">
         <is>
@@ -14905,7 +16768,88 @@
       <c r="GA23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="GB23" s="4" t="inlineStr">
+      <c r="GB23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD23" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH23" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ23" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL23" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC23" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14984,40 +16928,40 @@
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>71.7</v>
+        <v>79.7</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>71.7</v>
+        <v>79.2</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>66.7</v>
+        <v>73.7</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="W24" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="X24" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="Y24" s="7" t="n">
-        <v>53.6</v>
+        <v>72.7</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="Y24" s="6" t="n">
+        <v>57.6</v>
       </c>
       <c r="Z24" s="7" t="n">
-        <v>53.6</v>
+        <v>57.1</v>
       </c>
       <c r="AA24" s="7" t="n">
-        <v>45.8</v>
+        <v>48.8</v>
       </c>
       <c r="AB24" s="7" t="n">
-        <v>45.8</v>
+        <v>48.3</v>
       </c>
       <c r="AC24" s="7" t="n">
-        <v>41.8</v>
+        <v>42.8</v>
       </c>
       <c r="AD24" s="7" t="n">
         <v>41.8</v>
@@ -15065,7 +17009,7 @@
         <v>21.7</v>
       </c>
       <c r="AS24" s="3" t="n">
-        <v>230.73</v>
+        <v>231.45</v>
       </c>
       <c r="AT24" s="4" t="inlineStr">
         <is>
@@ -15505,7 +17449,88 @@
       <c r="GA24" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="GB24" s="4" t="inlineStr">
+      <c r="GB24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD24" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE24" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH24" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ24" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL24" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC24" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15584,40 +17609,40 @@
         </is>
       </c>
       <c r="R25" s="5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>60.5</v>
+        <v>67.5</v>
       </c>
       <c r="V25" s="5" t="n">
-        <v>60.5</v>
+        <v>66.5</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>51.7</v>
+        <v>56.7</v>
       </c>
       <c r="X25" s="7" t="n">
-        <v>51.7</v>
+        <v>56.2</v>
       </c>
       <c r="Y25" s="7" t="n">
-        <v>48.5</v>
+        <v>52.5</v>
       </c>
       <c r="Z25" s="7" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="AA25" s="7" t="n">
-        <v>41.3</v>
+        <v>44.3</v>
       </c>
       <c r="AB25" s="7" t="n">
-        <v>41.3</v>
+        <v>43.8</v>
       </c>
       <c r="AC25" s="8" t="n">
-        <v>37.8</v>
+        <v>38.8</v>
       </c>
       <c r="AD25" s="8" t="n">
         <v>37.8</v>
@@ -15665,7 +17690,7 @@
         <v>19.2</v>
       </c>
       <c r="AS25" s="3" t="n">
-        <v>227.05</v>
+        <v>227.77</v>
       </c>
       <c r="AT25" s="4" t="inlineStr">
         <is>
@@ -16105,7 +18130,88 @@
       <c r="GA25" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="GB25" s="4" t="inlineStr">
+      <c r="GB25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD25" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE25" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH25" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ25" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL25" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC25" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16184,40 +18290,40 @@
         </is>
       </c>
       <c r="R26" s="5" t="n">
-        <v>74.5</v>
+        <v>82.5</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>60.3</v>
+        <v>67.3</v>
       </c>
       <c r="V26" s="5" t="n">
-        <v>60.3</v>
+        <v>66.3</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>50.7</v>
+        <v>55.7</v>
       </c>
       <c r="X26" s="7" t="n">
-        <v>50.7</v>
+        <v>55.2</v>
       </c>
       <c r="Y26" s="7" t="n">
-        <v>47.1</v>
+        <v>51.1</v>
       </c>
       <c r="Z26" s="7" t="n">
-        <v>47.1</v>
+        <v>50.6</v>
       </c>
       <c r="AA26" s="7" t="n">
-        <v>40.6</v>
+        <v>43.6</v>
       </c>
       <c r="AB26" s="7" t="n">
-        <v>40.6</v>
+        <v>43.1</v>
       </c>
       <c r="AC26" s="8" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="AD26" s="8" t="n">
         <v>36.7</v>
@@ -16265,7 +18371,7 @@
         <v>20.4</v>
       </c>
       <c r="AS26" s="3" t="n">
-        <v>226.93</v>
+        <v>227.65</v>
       </c>
       <c r="AT26" s="4" t="inlineStr">
         <is>
@@ -16711,7 +18817,88 @@
       <c r="GA26" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="GB26" s="4" t="inlineStr">
+      <c r="GB26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD26" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH26" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ26" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC26" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16790,40 +18977,40 @@
         </is>
       </c>
       <c r="R27" s="5" t="n">
-        <v>75.5</v>
+        <v>83.5</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>68.3</v>
+        <v>76.3</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>68.3</v>
+        <v>75.8</v>
       </c>
       <c r="U27" s="5" t="n">
-        <v>62.8</v>
+        <v>69.8</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="W27" s="6" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="W27" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="Y27" s="6" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Z27" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="X27" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y27" s="7" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Z27" s="7" t="n">
-        <v>50.5</v>
-      </c>
       <c r="AA27" s="7" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB27" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="AC27" s="8" t="n">
-        <v>39.5</v>
+        <v>45.5</v>
+      </c>
+      <c r="AC27" s="7" t="n">
+        <v>40.5</v>
       </c>
       <c r="AD27" s="8" t="n">
         <v>39.5</v>
@@ -16871,7 +19058,7 @@
         <v>20.7</v>
       </c>
       <c r="AS27" s="3" t="n">
-        <v>223.54</v>
+        <v>224.26</v>
       </c>
       <c r="AT27" s="4" t="inlineStr">
         <is>
@@ -17311,7 +19498,88 @@
       <c r="GA27" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="GB27" s="4" t="inlineStr">
+      <c r="GB27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD27" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH27" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ27" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL27" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC27" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17390,40 +19658,40 @@
         </is>
       </c>
       <c r="R28" s="5" t="n">
-        <v>75.2</v>
+        <v>83.2</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>65.8</v>
+        <v>73.8</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>65.8</v>
+        <v>73.3</v>
       </c>
       <c r="U28" s="5" t="n">
-        <v>61.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="V28" s="5" t="n">
-        <v>61.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="W28" s="6" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="X28" s="7" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Y28" s="7" t="n">
         <v>50.4</v>
       </c>
-      <c r="X28" s="7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="Y28" s="7" t="n">
-        <v>46.4</v>
-      </c>
       <c r="Z28" s="7" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="AA28" s="8" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AB28" s="8" t="n">
-        <v>38.4</v>
+        <v>49.9</v>
+      </c>
+      <c r="AA28" s="7" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AB28" s="7" t="n">
+        <v>40.9</v>
       </c>
       <c r="AC28" s="8" t="n">
-        <v>33.4</v>
+        <v>34.4</v>
       </c>
       <c r="AD28" s="8" t="n">
         <v>33.4</v>
@@ -17471,7 +19739,7 @@
         <v>12.8</v>
       </c>
       <c r="AS28" s="3" t="n">
-        <v>222.21</v>
+        <v>222.93</v>
       </c>
       <c r="AT28" s="4" t="inlineStr">
         <is>
@@ -17911,7 +20179,88 @@
       <c r="GA28" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="GB28" s="4" t="inlineStr">
+      <c r="GB28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD28" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE28" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ28" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL28" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC28" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17990,40 +20339,40 @@
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>71.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>64.3</v>
+        <v>72.3</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="U29" s="6" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="V29" s="7" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="W29" s="7" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="Y29" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="X29" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="Y29" s="7" t="n">
-        <v>44.8</v>
-      </c>
       <c r="Z29" s="7" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="AA29" s="8" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="AB29" s="8" t="n">
-        <v>37.9</v>
+        <v>48.3</v>
+      </c>
+      <c r="AA29" s="7" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AB29" s="7" t="n">
+        <v>40.4</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>34.6</v>
+        <v>35.6</v>
       </c>
       <c r="AD29" s="8" t="n">
         <v>34.6</v>
@@ -18071,7 +20420,7 @@
         <v>17.8</v>
       </c>
       <c r="AS29" s="3" t="n">
-        <v>221.49</v>
+        <v>222.21</v>
       </c>
       <c r="AT29" s="4" t="inlineStr">
         <is>
@@ -18517,7 +20866,88 @@
       <c r="GA29" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="GB29" s="4" t="inlineStr">
+      <c r="GB29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD29" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF29" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH29" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ29" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL29" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC29" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18596,40 +21026,40 @@
         </is>
       </c>
       <c r="R30" s="5" t="n">
-        <v>72.3</v>
+        <v>80.3</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>62.3</v>
+        <v>70.3</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>62.3</v>
+        <v>69.8</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>58.7</v>
+        <v>65.7</v>
       </c>
       <c r="V30" s="5" t="n">
-        <v>58.7</v>
+        <v>64.7</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>48.1</v>
+        <v>53.1</v>
       </c>
       <c r="X30" s="7" t="n">
-        <v>48.1</v>
+        <v>52.6</v>
       </c>
       <c r="Y30" s="7" t="n">
-        <v>45.2</v>
+        <v>49.2</v>
       </c>
       <c r="Z30" s="7" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="AA30" s="8" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AB30" s="8" t="n">
-        <v>38.4</v>
+        <v>48.7</v>
+      </c>
+      <c r="AA30" s="7" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AB30" s="7" t="n">
+        <v>40.9</v>
       </c>
       <c r="AC30" s="8" t="n">
-        <v>34.3</v>
+        <v>35.3</v>
       </c>
       <c r="AD30" s="8" t="n">
         <v>34.3</v>
@@ -18677,7 +21107,7 @@
         <v>16.8</v>
       </c>
       <c r="AS30" s="3" t="n">
-        <v>220.75</v>
+        <v>221.47</v>
       </c>
       <c r="AT30" s="4" t="inlineStr">
         <is>
@@ -19123,7 +21553,88 @@
       <c r="GA30" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="GB30" s="4" t="inlineStr">
+      <c r="GB30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD30" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE30" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH30" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ30" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL30" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC30" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19202,40 +21713,40 @@
         </is>
       </c>
       <c r="R31" s="5" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="T31" s="7" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="U31" s="7" t="n">
-        <v>50.9</v>
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>57.9</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>50.9</v>
+        <v>56.9</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>41.7</v>
+        <v>46.7</v>
       </c>
       <c r="X31" s="7" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="Y31" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z31" s="8" t="n">
-        <v>39</v>
+        <v>46.2</v>
+      </c>
+      <c r="Y31" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z31" s="7" t="n">
+        <v>42.5</v>
       </c>
       <c r="AA31" s="8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AB31" s="8" t="n">
-        <v>34</v>
+        <v>36.5</v>
       </c>
       <c r="AC31" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD31" s="8" t="n">
         <v>31</v>
@@ -19283,7 +21794,7 @@
         <v>18.1</v>
       </c>
       <c r="AS31" s="3" t="n">
-        <v>219.62</v>
+        <v>220.34</v>
       </c>
       <c r="AT31" s="4" t="inlineStr">
         <is>
@@ -19723,14 +22234,95 @@
       <c r="GA31" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="GB31" s="4" t="inlineStr">
+      <c r="GB31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GC31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="GD31" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="GE31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="GF31" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="GG31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="GH31" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="GI31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="GJ31" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="GK31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="GL31" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="GM31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="GN31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GO31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GP31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GR31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GT31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GW31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GX31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="GZ31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HB31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC31" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:GB31"/>
+  <autoFilter ref="A1:HC31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>